--- a/bancos/SISOR/BASE_QDD_FISCAL_FONTE_95.xlsx
+++ b/bancos/SISOR/BASE_QDD_FISCAL_FONTE_95.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF68"/>
+  <dimension ref="A1:AF67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -580,41 +580,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B2" t="n">
-        <v>1070</v>
+        <v>1220</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS - GMG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>3</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
       <c r="F2" t="n">
-        <v>1071</v>
+        <v>1221</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS - GABINETE MILITAR</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
         <v>90</v>
       </c>
       <c r="K2" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="L2" t="n">
         <v>80</v>
@@ -622,55 +619,46 @@
       <c r="M2" t="n">
         <v>1</v>
       </c>
-      <c r="N2" t="n">
-        <v>11232</v>
-      </c>
       <c r="O2" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="P2" t="n">
-        <v>182</v>
+        <v>334</v>
       </c>
       <c r="Q2" t="n">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="T2" t="n">
-        <v>1008</v>
+        <v>1057</v>
       </c>
       <c r="U2" t="n">
         <v>1</v>
       </c>
-      <c r="V2" t="n">
-        <v>4950000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>14800000</v>
-      </c>
       <c r="X2" t="n">
-        <v>14800000</v>
+        <v>45000000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>PROJETO CONVIVÊNCIA COM A SECA E ESTIAGEM</t>
+          <t>CRÉDITO A EMPRESAS DA BACIA DO RIO DOCE</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>PROGRAMA ENCONTRO DAS ÁGUAS</t>
+          <t>MINAS EMPREENDEDORA: ESTADO MAIS SIMPLES E LIVRE PARA SE EMPREENDER</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -680,23 +668,23 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>INSTRUMENTO A SER CRIADO</t>
+          <t>9498928</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Disponibilização de acesso à água</t>
+          <t>Criação de fundo de disponibilização de crédito para recuperação econômica de pequenas, médias e grandes empresas nos municípios atingidos, além de fundo garantidor para facilitar o acesso a essa linha de crédito</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Disponibilização de acesso à água</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9498928 - Criação de fundo de disponibilização de crédito para recuperação econômica de pequenas, médias e grandes empresas nos municípios atingidos, além de fundo garantidor para facilitar o acesso a essa linha de crédito</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B3" t="n">
         <v>1220</v>
@@ -709,9 +697,6 @@
       <c r="D3" t="n">
         <v>3</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
       <c r="F3" t="n">
         <v>1221</v>
       </c>
@@ -721,16 +706,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
         <v>90</v>
       </c>
       <c r="K3" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="L3" t="n">
         <v>80</v>
@@ -738,55 +723,46 @@
       <c r="M3" t="n">
         <v>1</v>
       </c>
-      <c r="N3" t="n">
-        <v>10858</v>
-      </c>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="P3" t="n">
-        <v>127</v>
+        <v>334</v>
       </c>
       <c r="Q3" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="T3" t="n">
-        <v>1082</v>
+        <v>1059</v>
       </c>
       <c r="U3" t="n">
         <v>1</v>
       </c>
-      <c r="V3" t="n">
-        <v>92880</v>
-      </c>
-      <c r="W3" t="n">
-        <v>92880</v>
-      </c>
       <c r="X3" t="n">
-        <v>92880</v>
+        <v>33921382</v>
       </c>
       <c r="Y3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>MINAS REURB SEDE</t>
+          <t>GARANTIA DE CRÉDITOS A EMPRESAS DA BACIA DO RIO DOCE</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>POLÍTICA DE REGULARIZAÇÃO FUNDIÁRIA E DE GESTÃO DE IMÓVEIS</t>
+          <t>MINAS EMPREENDEDORA: ESTADO MAIS SIMPLES E LIVRE PARA SE EMPREENDER</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -794,23 +770,25 @@
           <t>ANEXO 12</t>
         </is>
       </c>
-      <c r="AD3" t="n">
-        <v>9473171</v>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>9498928</t>
+        </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>Promoção de regularização fundiária</t>
+          <t>Criação de fundo de disponibilização de crédito para recuperação econômica de pequenas, médias e grandes empresas nos municípios atingidos, além de fundo garantidor para facilitar o acesso a essa linha de crédito</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9473171 - Promoção de regularização fundiária</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9498928 - Criação de fundo de disponibilização de crédito para recuperação econômica de pequenas, médias e grandes empresas nos municípios atingidos, além de fundo garantidor para facilitar o acesso a essa linha de crédito</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B4" t="n">
         <v>1220</v>
@@ -823,9 +801,6 @@
       <c r="D4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
       <c r="F4" t="n">
         <v>1221</v>
       </c>
@@ -841,10 +816,10 @@
         <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="K4" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="L4" t="n">
         <v>80</v>
@@ -852,55 +827,46 @@
       <c r="M4" t="n">
         <v>1</v>
       </c>
-      <c r="N4" t="n">
-        <v>10858</v>
-      </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="P4" t="n">
-        <v>127</v>
+        <v>691</v>
       </c>
       <c r="Q4" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="T4" t="n">
-        <v>1082</v>
+        <v>1056</v>
       </c>
       <c r="U4" t="n">
         <v>1</v>
       </c>
-      <c r="V4" t="n">
-        <v>39145000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>39145000</v>
-      </c>
       <c r="X4" t="n">
-        <v>39145000</v>
+        <v>7127598</v>
       </c>
       <c r="Y4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>MINAS REURB SEDE</t>
+          <t>FOMENTO  AO COOPERATIVISMO, ASSOCIATIVISMO E ÀS MICRO E PEQUENAS EMPRESAS DA BACIA DO RIO DOCE (COOPERA + RIO DOCE)</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>POLÍTICA DE REGULARIZAÇÃO FUNDIÁRIA E DE GESTÃO DE IMÓVEIS</t>
+          <t>MINAS EMPREENDEDORA: ESTADO MAIS SIMPLES E LIVRE PARA SE EMPREENDER</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -908,23 +874,25 @@
           <t>ANEXO 12</t>
         </is>
       </c>
-      <c r="AD4" t="n">
-        <v>9473171</v>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>9480259</t>
+        </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Promoção de regularização fundiária</t>
+          <t>Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9473171 - Promoção de regularização fundiária</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9480259 - Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B5" t="n">
         <v>1220</v>
@@ -937,9 +905,6 @@
       <c r="D5" t="n">
         <v>3</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
       <c r="F5" t="n">
         <v>1221</v>
       </c>
@@ -958,7 +923,7 @@
         <v>90</v>
       </c>
       <c r="K5" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="L5" t="n">
         <v>80</v>
@@ -966,55 +931,46 @@
       <c r="M5" t="n">
         <v>1</v>
       </c>
-      <c r="N5" t="n">
-        <v>10858</v>
-      </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="P5" t="n">
-        <v>127</v>
+        <v>691</v>
       </c>
       <c r="Q5" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="T5" t="n">
-        <v>1082</v>
+        <v>1056</v>
       </c>
       <c r="U5" t="n">
         <v>1</v>
       </c>
-      <c r="V5" t="n">
-        <v>993696</v>
-      </c>
-      <c r="W5" t="n">
-        <v>993696</v>
-      </c>
       <c r="X5" t="n">
-        <v>993696</v>
+        <v>130820</v>
       </c>
       <c r="Y5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>MINAS REURB SEDE</t>
+          <t>FOMENTO  AO COOPERATIVISMO, ASSOCIATIVISMO E ÀS MICRO E PEQUENAS EMPRESAS DA BACIA DO RIO DOCE (COOPERA + RIO DOCE)</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>POLÍTICA DE REGULARIZAÇÃO FUNDIÁRIA E DE GESTÃO DE IMÓVEIS</t>
+          <t>MINAS EMPREENDEDORA: ESTADO MAIS SIMPLES E LIVRE PARA SE EMPREENDER</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1022,23 +978,25 @@
           <t>ANEXO 12</t>
         </is>
       </c>
-      <c r="AD5" t="n">
-        <v>9473171</v>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>9480259</t>
+        </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Promoção de regularização fundiária</t>
+          <t>Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9473171 - Promoção de regularização fundiária</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9480259 - Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B6" t="n">
         <v>1220</v>
@@ -1051,9 +1009,6 @@
       <c r="D6" t="n">
         <v>3</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
       <c r="F6" t="n">
         <v>1221</v>
       </c>
@@ -1072,7 +1027,7 @@
         <v>90</v>
       </c>
       <c r="K6" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="L6" t="n">
         <v>80</v>
@@ -1080,55 +1035,46 @@
       <c r="M6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" t="n">
-        <v>10858</v>
-      </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="P6" t="n">
-        <v>127</v>
+        <v>691</v>
       </c>
       <c r="Q6" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="T6" t="n">
-        <v>1082</v>
+        <v>1056</v>
       </c>
       <c r="U6" t="n">
         <v>1</v>
       </c>
-      <c r="V6" t="n">
-        <v>269632</v>
-      </c>
-      <c r="W6" t="n">
-        <v>269632</v>
-      </c>
       <c r="X6" t="n">
-        <v>269632</v>
+        <v>417087</v>
       </c>
       <c r="Y6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>MINAS REURB SEDE</t>
+          <t>FOMENTO  AO COOPERATIVISMO, ASSOCIATIVISMO E ÀS MICRO E PEQUENAS EMPRESAS DA BACIA DO RIO DOCE (COOPERA + RIO DOCE)</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>POLÍTICA DE REGULARIZAÇÃO FUNDIÁRIA E DE GESTÃO DE IMÓVEIS</t>
+          <t>MINAS EMPREENDEDORA: ESTADO MAIS SIMPLES E LIVRE PARA SE EMPREENDER</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1136,23 +1082,25 @@
           <t>ANEXO 12</t>
         </is>
       </c>
-      <c r="AD6" t="n">
-        <v>9473171</v>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>9480259</t>
+        </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>Promoção de regularização fundiária</t>
+          <t>Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9473171 - Promoção de regularização fundiária</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9480259 - Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B7" t="n">
         <v>1220</v>
@@ -1165,9 +1113,6 @@
       <c r="D7" t="n">
         <v>3</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
       <c r="F7" t="n">
         <v>1221</v>
       </c>
@@ -1186,7 +1131,7 @@
         <v>90</v>
       </c>
       <c r="K7" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="L7" t="n">
         <v>80</v>
@@ -1194,55 +1139,46 @@
       <c r="M7" t="n">
         <v>1</v>
       </c>
-      <c r="N7" t="n">
-        <v>10858</v>
-      </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="P7" t="n">
-        <v>127</v>
+        <v>691</v>
       </c>
       <c r="Q7" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="T7" t="n">
-        <v>1082</v>
+        <v>1056</v>
       </c>
       <c r="U7" t="n">
         <v>1</v>
       </c>
-      <c r="V7" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="W7" t="n">
-        <v>7000000</v>
-      </c>
       <c r="X7" t="n">
-        <v>7000000</v>
+        <v>1145356</v>
       </c>
       <c r="Y7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>MINAS REURB SEDE</t>
+          <t>FOMENTO  AO COOPERATIVISMO, ASSOCIATIVISMO E ÀS MICRO E PEQUENAS EMPRESAS DA BACIA DO RIO DOCE (COOPERA + RIO DOCE)</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>POLÍTICA DE REGULARIZAÇÃO FUNDIÁRIA E DE GESTÃO DE IMÓVEIS</t>
+          <t>MINAS EMPREENDEDORA: ESTADO MAIS SIMPLES E LIVRE PARA SE EMPREENDER</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1250,23 +1186,25 @@
           <t>ANEXO 12</t>
         </is>
       </c>
-      <c r="AD7" t="n">
-        <v>9473171</v>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>9468055</t>
+        </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>Promoção de regularização fundiária</t>
+          <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas.</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9473171 - Promoção de regularização fundiária</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9468055 - Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B8" t="n">
         <v>1220</v>
@@ -1279,9 +1217,6 @@
       <c r="D8" t="n">
         <v>3</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
       <c r="F8" t="n">
         <v>1221</v>
       </c>
@@ -1291,16 +1226,16 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>90</v>
       </c>
       <c r="K8" t="n">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="L8" t="n">
         <v>80</v>
@@ -1308,14 +1243,11 @@
       <c r="M8" t="n">
         <v>1</v>
       </c>
-      <c r="N8" t="n">
-        <v>11264</v>
-      </c>
       <c r="O8" t="n">
         <v>23</v>
       </c>
       <c r="P8" t="n">
-        <v>334</v>
+        <v>691</v>
       </c>
       <c r="Q8" t="n">
         <v>132</v>
@@ -1324,29 +1256,23 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T8" t="n">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="U8" t="n">
         <v>1</v>
       </c>
-      <c r="V8" t="n">
-        <v>40200000</v>
-      </c>
-      <c r="W8" t="n">
-        <v>40200000</v>
-      </c>
       <c r="X8" t="n">
-        <v>40200000</v>
+        <v>185230</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>CRÉDITO A EMPRESAS DA BACIA DO RIO DOCE</t>
+          <t>FOMENTO  AO COOPERATIVISMO, ASSOCIATIVISMO E ÀS MICRO E PEQUENAS EMPRESAS DA BACIA DO RIO DOCE (COOPERA + RIO DOCE)</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1356,7 +1282,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1366,23 +1292,23 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>INSTRUMENTO A SER CRIADO</t>
+          <t>9480259</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>Criação de fundo de disponibilização de crédito para recuperação econômica de pequenas, médias e grandes empresas dos municípios atingidos, além de fundo garantidor para facilitar o acesso a essa linha de crédito</t>
+          <t>Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Criação de fundo de disponibilização de crédito para recuperação econômica de pequenas, médias e grandes empresas dos municípios atingidos, além de fundo garantidor para facilitar o acesso a essa linha de crédito</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9480259 - Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B9" t="n">
         <v>1220</v>
@@ -1395,9 +1321,6 @@
       <c r="D9" t="n">
         <v>3</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
       <c r="F9" t="n">
         <v>1221</v>
       </c>
@@ -1410,13 +1333,13 @@
         <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="K9" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="L9" t="n">
         <v>80</v>
@@ -1424,14 +1347,11 @@
       <c r="M9" t="n">
         <v>1</v>
       </c>
-      <c r="N9" t="n">
-        <v>11265</v>
-      </c>
       <c r="O9" t="n">
         <v>23</v>
       </c>
       <c r="P9" t="n">
-        <v>334</v>
+        <v>691</v>
       </c>
       <c r="Q9" t="n">
         <v>132</v>
@@ -1440,29 +1360,23 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="T9" t="n">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="U9" t="n">
         <v>1</v>
       </c>
-      <c r="V9" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="W9" t="n">
-        <v>30000000</v>
-      </c>
       <c r="X9" t="n">
-        <v>30000000</v>
+        <v>3000000</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>GARANTIA DE CRÉDITOS A EMPRESAS DA BACIA DO RIO DOCE</t>
+          <t>FOMENTO  AO COOPERATIVISMO, ASSOCIATIVISMO E ÀS MICRO E PEQUENAS EMPRESAS DA BACIA DO RIO DOCE (COOPERA + RIO DOCE)</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1472,7 +1386,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1482,23 +1396,23 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>INSTRUMENTO A SER CRIADO</t>
+          <t>9480259</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>Criação de fundo de disponibilização de crédito para recuperação econômica de pequenas, médias e grandes empresas dos municípios atingidos, além de fundo garantidor para facilitar o acesso a essa linha de crédito</t>
+          <t>Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Criação de fundo de disponibilização de crédito para recuperação econômica de pequenas, médias e grandes empresas dos municípios atingidos, além de fundo garantidor para facilitar o acesso a essa linha de crédito</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9480259 - Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B10" t="n">
         <v>1220</v>
@@ -1511,9 +1425,6 @@
       <c r="D10" t="n">
         <v>3</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
       <c r="F10" t="n">
         <v>1221</v>
       </c>
@@ -1540,55 +1451,46 @@
       <c r="M10" t="n">
         <v>1</v>
       </c>
-      <c r="N10" t="n">
-        <v>11250</v>
-      </c>
       <c r="O10" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>691</v>
+        <v>127</v>
       </c>
       <c r="Q10" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="T10" t="n">
-        <v>1056</v>
+        <v>1082</v>
       </c>
       <c r="U10" t="n">
         <v>1</v>
       </c>
-      <c r="V10" t="n">
-        <v>272500</v>
-      </c>
-      <c r="W10" t="n">
-        <v>272500</v>
-      </c>
       <c r="X10" t="n">
-        <v>272500</v>
+        <v>30960</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>FOMENTO AO COOPERATIVISMO, ASSOCIATIVISMO E ÀS MICRO E PEQUENAS EMPRESAS DA BACIA DO RIO DOCE (COOPERA + RIO DOCE)</t>
+          <t>MINAS REURB SEDE</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>MINAS EMPREENDEDORA: ESTADO MAIS SIMPLES E LIVRE PARA SE EMPREENDER</t>
+          <t>POLÍTICA DE REGULARIZAÇÃO FUNDIÁRIA E DE GESTÃO DE IMÓVEIS</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1598,23 +1500,23 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>INSTRUMENTO A SER CRIADO</t>
+          <t>9473171</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
+          <t>Promoção da regularização fundiária</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9473171 - Promoção da regularização fundiária</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B11" t="n">
         <v>1220</v>
@@ -1627,9 +1529,6 @@
       <c r="D11" t="n">
         <v>3</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
       <c r="F11" t="n">
         <v>1221</v>
       </c>
@@ -1648,7 +1547,7 @@
         <v>90</v>
       </c>
       <c r="K11" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="L11" t="n">
         <v>80</v>
@@ -1656,55 +1555,46 @@
       <c r="M11" t="n">
         <v>1</v>
       </c>
-      <c r="N11" t="n">
-        <v>11250</v>
-      </c>
       <c r="O11" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>691</v>
+        <v>127</v>
       </c>
       <c r="Q11" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="T11" t="n">
-        <v>1056</v>
+        <v>1082</v>
       </c>
       <c r="U11" t="n">
         <v>1</v>
       </c>
-      <c r="V11" t="n">
-        <v>322501</v>
-      </c>
-      <c r="W11" t="n">
-        <v>322501</v>
-      </c>
       <c r="X11" t="n">
-        <v>322501</v>
+        <v>110000</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>FOMENTO AO COOPERATIVISMO, ASSOCIATIVISMO E ÀS MICRO E PEQUENAS EMPRESAS DA BACIA DO RIO DOCE (COOPERA + RIO DOCE)</t>
+          <t>MINAS REURB SEDE</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>MINAS EMPREENDEDORA: ESTADO MAIS SIMPLES E LIVRE PARA SE EMPREENDER</t>
+          <t>POLÍTICA DE REGULARIZAÇÃO FUNDIÁRIA E DE GESTÃO DE IMÓVEIS</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1714,23 +1604,23 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>INSTRUMENTO A SER CRIADO</t>
+          <t>9473171</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
+          <t>Promoção da regularização fundiária</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9473171 - Promoção da regularização fundiária</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B12" t="n">
         <v>1220</v>
@@ -1743,9 +1633,6 @@
       <c r="D12" t="n">
         <v>3</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
       <c r="F12" t="n">
         <v>1221</v>
       </c>
@@ -1764,7 +1651,7 @@
         <v>90</v>
       </c>
       <c r="K12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L12" t="n">
         <v>80</v>
@@ -1772,55 +1659,46 @@
       <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="N12" t="n">
-        <v>11250</v>
-      </c>
       <c r="O12" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>691</v>
+        <v>127</v>
       </c>
       <c r="Q12" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="T12" t="n">
-        <v>1056</v>
+        <v>1082</v>
       </c>
       <c r="U12" t="n">
         <v>1</v>
       </c>
-      <c r="V12" t="n">
-        <v>5678875</v>
-      </c>
-      <c r="W12" t="n">
-        <v>5678875</v>
-      </c>
       <c r="X12" t="n">
-        <v>5678875</v>
+        <v>1360324</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>FOMENTO AO COOPERATIVISMO, ASSOCIATIVISMO E ÀS MICRO E PEQUENAS EMPRESAS DA BACIA DO RIO DOCE (COOPERA + RIO DOCE)</t>
+          <t>MINAS REURB SEDE</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>MINAS EMPREENDEDORA: ESTADO MAIS SIMPLES E LIVRE PARA SE EMPREENDER</t>
+          <t>POLÍTICA DE REGULARIZAÇÃO FUNDIÁRIA E DE GESTÃO DE IMÓVEIS</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1830,23 +1708,23 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>INSTRUMENTO A SER CRIADO</t>
+          <t>9473171</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
+          <t>Promoção da regularização fundiária</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9473171 - Promoção da regularização fundiária</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B13" t="n">
         <v>1220</v>
@@ -1859,9 +1737,6 @@
       <c r="D13" t="n">
         <v>3</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
       <c r="F13" t="n">
         <v>1221</v>
       </c>
@@ -1880,7 +1755,7 @@
         <v>90</v>
       </c>
       <c r="K13" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L13" t="n">
         <v>80</v>
@@ -1888,55 +1763,46 @@
       <c r="M13" t="n">
         <v>1</v>
       </c>
-      <c r="N13" t="n">
-        <v>11250</v>
-      </c>
       <c r="O13" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>691</v>
+        <v>127</v>
       </c>
       <c r="Q13" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="T13" t="n">
-        <v>1056</v>
+        <v>1082</v>
       </c>
       <c r="U13" t="n">
         <v>1</v>
       </c>
-      <c r="V13" t="n">
-        <v>470000</v>
-      </c>
-      <c r="W13" t="n">
-        <v>470000</v>
-      </c>
       <c r="X13" t="n">
-        <v>470000</v>
+        <v>102974</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>FOMENTO AO COOPERATIVISMO, ASSOCIATIVISMO E ÀS MICRO E PEQUENAS EMPRESAS DA BACIA DO RIO DOCE (COOPERA + RIO DOCE)</t>
+          <t>MINAS REURB SEDE</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>MINAS EMPREENDEDORA: ESTADO MAIS SIMPLES E LIVRE PARA SE EMPREENDER</t>
+          <t>POLÍTICA DE REGULARIZAÇÃO FUNDIÁRIA E DE GESTÃO DE IMÓVEIS</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -1946,44 +1812,41 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>INSTRUMENTO A SER CRIADO</t>
+          <t>9473171</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
+          <t>Promoção da regularização fundiária</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9473171 - Promoção da regularização fundiária</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B14" t="n">
-        <v>1220</v>
+        <v>1230</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>3</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
       <c r="F14" t="n">
-        <v>1221</v>
+        <v>1231</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1993,10 +1856,10 @@
         <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="K14" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L14" t="n">
         <v>80</v>
@@ -2004,55 +1867,46 @@
       <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="N14" t="n">
-        <v>11250</v>
-      </c>
       <c r="O14" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="P14" t="n">
-        <v>691</v>
+        <v>122</v>
       </c>
       <c r="Q14" t="n">
-        <v>132</v>
+        <v>705</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>56</v>
+        <v>500</v>
       </c>
       <c r="T14" t="n">
-        <v>1056</v>
+        <v>2500</v>
       </c>
       <c r="U14" t="n">
         <v>1</v>
       </c>
-      <c r="V14" t="n">
-        <v>2960000</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2960000</v>
-      </c>
       <c r="X14" t="n">
-        <v>2960000</v>
+        <v>1548466</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>FOMENTO AO COOPERATIVISMO, ASSOCIATIVISMO E ÀS MICRO E PEQUENAS EMPRESAS DA BACIA DO RIO DOCE (COOPERA + RIO DOCE)</t>
+          <t>ASSESSORAMENTO E GERENCIAMENTO DE POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>MINAS EMPREENDEDORA: ESTADO MAIS SIMPLES E LIVRE PARA SE EMPREENDER</t>
+          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2062,57 +1916,54 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>INSTRUMENTO A SER CRIADO</t>
+          <t>9456616</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
+          <t>Zoneamento Ambiental e Produtivo-ZAP</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9456616 - Zoneamento Ambiental e Produtivo-ZAP</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B15" t="n">
-        <v>1220</v>
+        <v>1230</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>3</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
       <c r="F15" t="n">
-        <v>1221</v>
+        <v>1231</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
         <v>90</v>
       </c>
       <c r="K15" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="L15" t="n">
         <v>80</v>
@@ -2120,55 +1971,46 @@
       <c r="M15" t="n">
         <v>1</v>
       </c>
-      <c r="N15" t="n">
-        <v>11250</v>
-      </c>
       <c r="O15" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="P15" t="n">
-        <v>691</v>
+        <v>122</v>
       </c>
       <c r="Q15" t="n">
-        <v>132</v>
+        <v>705</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S15" t="n">
-        <v>56</v>
+        <v>500</v>
       </c>
       <c r="T15" t="n">
-        <v>1056</v>
+        <v>2500</v>
       </c>
       <c r="U15" t="n">
         <v>1</v>
       </c>
-      <c r="V15" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="W15" t="n">
-        <v>4000000</v>
-      </c>
       <c r="X15" t="n">
-        <v>4000000</v>
+        <v>398431</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>FOMENTO AO COOPERATIVISMO, ASSOCIATIVISMO E ÀS MICRO E PEQUENAS EMPRESAS DA BACIA DO RIO DOCE (COOPERA + RIO DOCE)</t>
+          <t>ASSESSORAMENTO E GERENCIAMENTO DE POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>MINAS EMPREENDEDORA: ESTADO MAIS SIMPLES E LIVRE PARA SE EMPREENDER</t>
+          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2178,23 +2020,23 @@
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>INSTRUMENTO A SER CRIADO</t>
+          <t>9468055</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
+          <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação de iniciativas</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Fomento ao associativismo e ao cooperativismo a partir de assessoria às organizações, podendo incluir aprimoramento da gestão, qualificação de produtos e serviços, apoio na comunicação e marketing, mapeamento de necessidades de infraestrutura e fornecimento de equipamentos e insumos</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9468055 - Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação de iniciativas</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B16" t="n">
         <v>1230</v>
@@ -2207,9 +2049,6 @@
       <c r="D16" t="n">
         <v>3</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
       <c r="F16" t="n">
         <v>1231</v>
       </c>
@@ -2228,7 +2067,7 @@
         <v>90</v>
       </c>
       <c r="K16" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L16" t="n">
         <v>80</v>
@@ -2236,115 +2075,103 @@
       <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="N16" t="n">
-        <v>9559</v>
-      </c>
       <c r="O16" t="n">
         <v>20</v>
       </c>
       <c r="P16" t="n">
-        <v>122</v>
+        <v>608</v>
       </c>
       <c r="Q16" t="n">
-        <v>705</v>
+        <v>111</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S16" t="n">
-        <v>500</v>
+        <v>383</v>
       </c>
       <c r="T16" t="n">
-        <v>2500</v>
+        <v>4383</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
       </c>
-      <c r="V16" t="n">
-        <v>440000</v>
-      </c>
-      <c r="W16" t="n">
-        <v>440000</v>
-      </c>
       <c r="X16" t="n">
-        <v>440000</v>
+        <v>30304835</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>ASSESSORAMENTO E GERENCIAMENTO DE POLÍTICAS PÚBLICAS</t>
+          <t>DESENVOLVIMENTO RURAL SUSTENTÁVEL E AGRICULTURA FAMILIAR</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+          <t>DESENVOLVIMENTO DAS CADEIAS PRODUTIVAS DA AGROPECUÁRIA</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ANEXO 10</t>
+          <t>ANEXO 12</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>INSTRUMENTO A SER CRIADO</t>
+          <t>9498925</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>Fortalecimento dos Serviços de Inspeção Municipais</t>
+          <t xml:space="preserve"> Oferta de serviços de assistência técnica e extensão rural (metodologia ISA/PASEA), visando à produção de alimentos e estímulo à comercialização e adequação socioeconômica e ambiental de propriedades rurais</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 10 - INSTRUMENTO A SER CRIADO - Fortalecimento dos Serviços de Inspeção Municipais</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9498925 -  Oferta de serviços de assistência técnica e extensão rural (metodologia ISA/PASEA), visando à produção de alimentos e estímulo à comercialização e adequação socioeconômica e ambiental de propriedades rurais</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B17" t="n">
         <v>1230</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - IMA</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>3</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
       <c r="F17" t="n">
-        <v>1231</v>
+        <v>2371</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
+          <t>INSTITUTO MINEIRO DE AGROPECUÁRIA - IMA</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J17" t="n">
         <v>90</v>
       </c>
       <c r="K17" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="L17" t="n">
         <v>80</v>
@@ -2352,55 +2179,46 @@
       <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="N17" t="n">
-        <v>10674</v>
-      </c>
       <c r="O17" t="n">
         <v>20</v>
       </c>
       <c r="P17" t="n">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="Q17" t="n">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="R17" t="n">
         <v>4</v>
       </c>
       <c r="S17" t="n">
-        <v>358</v>
+        <v>238</v>
       </c>
       <c r="T17" t="n">
-        <v>4358</v>
+        <v>4238</v>
       </c>
       <c r="U17" t="n">
         <v>1</v>
       </c>
-      <c r="V17" t="n">
-        <v>2132231</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2132231</v>
-      </c>
       <c r="X17" t="n">
-        <v>2132231</v>
+        <v>8311374</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>CIRCUITOS DE COMERCIALIZAÇÃO E MERCADOS INSTITUCIONAIS</t>
+          <t>REESTRUTURAÇÃO DO LABORATÓRIO DE QUÍMICA AGROPECUÁRIA DO INSTITUTO MINEIRO DE AGROPECUÁRIA.</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>ACESSO A MERCADOS</t>
+          <t>DEFESA SANITÁRIA</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2410,57 +2228,54 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>INSTRUMENTO A SER CRIADO</t>
+          <t>9484149</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>Circuitos De Comercialização E Mercados Institucionais</t>
+          <t>Reestruturação física e ampliação tecnológica dos laboratórios para atendimento a segurança alimentar</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 10 - INSTRUMENTO A SER CRIADO - Circuitos De Comercialização E Mercados Institucionais</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 10 - 9484149 - Reestruturação física e ampliação tecnológica dos laboratórios para atendimento a segurança alimentar</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B18" t="n">
-        <v>1230</v>
+        <v>1250</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
+          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS - PMMG</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>3</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
       <c r="F18" t="n">
-        <v>1231</v>
+        <v>1251</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
+          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS - PMMG</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="K18" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="L18" t="n">
         <v>80</v>
@@ -2468,55 +2283,46 @@
       <c r="M18" t="n">
         <v>1</v>
       </c>
-      <c r="N18" t="n">
-        <v>10720</v>
-      </c>
       <c r="O18" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="P18" t="n">
-        <v>608</v>
+        <v>181</v>
       </c>
       <c r="Q18" t="n">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="R18" t="n">
         <v>4</v>
       </c>
       <c r="S18" t="n">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="T18" t="n">
-        <v>4383</v>
+        <v>4365</v>
       </c>
       <c r="U18" t="n">
         <v>1</v>
       </c>
-      <c r="V18" t="n">
-        <v>1634900</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1634900</v>
-      </c>
       <c r="X18" t="n">
-        <v>1634900</v>
+        <v>1214845</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>DESENVOLVIMENTO RURAL SUSTENTÁVEL E AGRICULTURA FAMILIAR</t>
+          <t>POLICIAMENTO OSTENSIVO GERAL</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>DESENVOLVIMENTO DAS CADEIAS PRODUTIVAS DA AGROPECUÁRIA</t>
+          <t>POLÍCIA OSTENSIVA</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2524,57 +2330,56 @@
           <t>ANEXO 12</t>
         </is>
       </c>
-      <c r="AD18" t="n">
-        <v>9456616</v>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>9456627</t>
+        </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>Atualização e realização de novos estudos de Zoneamento Ambiental Produtivo em sub-bacias hidrográficas da Bacia Hidrográfica do rio Doce</t>
+          <t>Adequação e equipagem de Bases de Segurança Pública (PMMG, CBMMG e PCMG) no Município de Mariana/MG</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456616 - Atualização e realização de novos estudos de Zoneamento Ambiental Produtivo em sub-bacias hidrográficas da Bacia Hidrográfica do rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9456627 - Adequação e equipagem de Bases de Segurança Pública (PMMG, CBMMG e PCMG) no Município de Mariana/MG</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B19" t="n">
-        <v>1230</v>
+        <v>1300</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - DER-MG</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>3</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
       <c r="F19" t="n">
-        <v>1231</v>
+        <v>2301</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS - DER-MG</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J19" t="n">
         <v>90</v>
       </c>
       <c r="K19" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="L19" t="n">
         <v>80</v>
@@ -2582,102 +2387,90 @@
       <c r="M19" t="n">
         <v>1</v>
       </c>
-      <c r="N19" t="n">
-        <v>10720</v>
-      </c>
       <c r="O19" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="P19" t="n">
-        <v>608</v>
+        <v>782</v>
       </c>
       <c r="Q19" t="n">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="R19" t="n">
         <v>4</v>
       </c>
       <c r="S19" t="n">
-        <v>383</v>
+        <v>268</v>
       </c>
       <c r="T19" t="n">
-        <v>4383</v>
+        <v>4268</v>
       </c>
       <c r="U19" t="n">
         <v>1</v>
       </c>
-      <c r="V19" t="n">
-        <v>407776</v>
-      </c>
-      <c r="W19" t="n">
-        <v>407776</v>
-      </c>
       <c r="X19" t="n">
-        <v>407776</v>
+        <v>10000000</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>DESENVOLVIMENTO RURAL SUSTENTÁVEL E AGRICULTURA FAMILIAR</t>
+          <t>AMPLIAÇÃO DE CAPACIDADE DA MALHA VIÁRIA E RESTAURAÇÃO DO PAVIMENTO</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>DESENVOLVIMENTO DAS CADEIAS PRODUTIVAS DA AGROPECUÁRIA</t>
+          <t>DESENVOLVIMENTO SUSTENTÁVEL DA INFRAESTRUTURA RODOVIÁRIA</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ANEXO 10</t>
+          <t>ANEXO 12</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>INSTRUMENTO A SER CRIADO</t>
+          <t>9452379</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>Arranjo Produtivo Local Projeto Apicultura</t>
+          <t>AMPLIAÇÃO E MELHORIA NA PAVIMENTAÇÃO, MANUTENÇÃO E RECUPERAÇÃO FUNCIONAL DA INFRAESTRUTURA VIÁRIA</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 10 - INSTRUMENTO A SER CRIADO - Arranjo Produtivo Local Projeto Apicultura</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9452379 - AMPLIAÇÃO E MELHORIA NA PAVIMENTAÇÃO, MANUTENÇÃO E RECUPERAÇÃO FUNCIONAL DA INFRAESTRUTURA VIÁRIA</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B20" t="n">
-        <v>1230</v>
+        <v>1300</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - DER-MG</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>3</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
       <c r="F20" t="n">
-        <v>1231</v>
+        <v>2301</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS - DER-MG</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -2690,7 +2483,7 @@
         <v>90</v>
       </c>
       <c r="K20" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L20" t="n">
         <v>80</v>
@@ -2698,55 +2491,46 @@
       <c r="M20" t="n">
         <v>1</v>
       </c>
-      <c r="N20" t="n">
-        <v>10764</v>
-      </c>
       <c r="O20" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="P20" t="n">
-        <v>608</v>
+        <v>782</v>
       </c>
       <c r="Q20" t="n">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="R20" t="n">
         <v>4</v>
       </c>
       <c r="S20" t="n">
-        <v>420</v>
+        <v>275</v>
       </c>
       <c r="T20" t="n">
-        <v>4420</v>
+        <v>4275</v>
       </c>
       <c r="U20" t="n">
         <v>1</v>
       </c>
-      <c r="V20" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="W20" t="n">
-        <v>30000000</v>
-      </c>
       <c r="X20" t="n">
-        <v>30000000</v>
+        <v>126182023</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>MECANIZAÇÃO NO CAMPO</t>
+          <t>IMPLANTAÇÃO/PAVIMENTAÇÃO DA MALHA</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>DESENVOLVIMENTO DAS CADEIAS PRODUTIVAS DA AGROPECUÁRIA</t>
+          <t>DESENVOLVIMENTO SUSTENTÁVEL DA INFRAESTRUTURA RODOVIÁRIA</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2754,57 +2538,56 @@
           <t>ANEXO 12</t>
         </is>
       </c>
-      <c r="AD20" t="n">
-        <v>9474703</v>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>9452379</t>
+        </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>Adequação de infraestrutura em áreas rurais</t>
+          <t>AMPLIAÇÃO E MELHORIA NA PAVIMENTAÇÃO, MANUTENÇÃO E RECUPERAÇÃO FUNCIONAL DA INFRAESTRUTURA VIÁRIA</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9474703 - Adequação de infraestrutura em áreas rurais</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9452379 - AMPLIAÇÃO E MELHORIA NA PAVIMENTAÇÃO, MANUTENÇÃO E RECUPERAÇÃO FUNCIONAL DA INFRAESTRUTURA VIÁRIA</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B21" t="n">
-        <v>1230</v>
+        <v>1300</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - FPP - MG</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>3</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
       <c r="F21" t="n">
-        <v>1231</v>
+        <v>4631</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
+          <t>FUNDO DE PAGAMENTO DE PARCERIAS PÚBLICO - PRIVADAS DE MINAS GERAIS - FPP - MG</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J21" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="K21" t="n">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="L21" t="n">
         <v>80</v>
@@ -2812,115 +2595,103 @@
       <c r="M21" t="n">
         <v>1</v>
       </c>
-      <c r="N21" t="n">
-        <v>10744</v>
-      </c>
       <c r="O21" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>608</v>
+        <v>130</v>
       </c>
       <c r="Q21" t="n">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="R21" t="n">
         <v>4</v>
       </c>
       <c r="S21" t="n">
-        <v>403</v>
+        <v>128</v>
       </c>
       <c r="T21" t="n">
-        <v>4403</v>
+        <v>4128</v>
       </c>
       <c r="U21" t="n">
         <v>1</v>
       </c>
-      <c r="V21" t="n">
-        <v>5641567</v>
-      </c>
-      <c r="W21" t="n">
-        <v>5641567</v>
-      </c>
       <c r="X21" t="n">
-        <v>5641567</v>
+        <v>322000000</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>MINAS AGROINDÚSTRIA</t>
+          <t>LOTE OURO PRETO</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>CERTIFICAÇÕES E HABILITAÇÕES DE PRODUTOS AGROPECUÁRIOS E AGROINDUSTRIAIS</t>
+          <t>PROMOÇÃO DE CONCESSÕES E PARCERIAS</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ANEXO 10</t>
+          <t>ANEXO 13</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>INSTRUMENTO A SER CRIADO</t>
+          <t>9445763</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>Fortalecimento dos Serviços de Inspeção Municipais</t>
+          <t>OBRAS E SERVIÇOS PARA CONSTRUÇÃO E IMPLANTAÇÃO DE MELHORIAS RODOVIÁRIAS, OPERAÇÃO E MANUTENÇÃO DAS RODOVIAS DO LOTE OURO PRETO – MARIANA, COM PRIORIZAÇÃO DE DUPLICAÇÃO DA BR-356, DO ENTRONCAMENTO COM A BR-040 ATÉ O ENTRONCAMENTO COM A RODOVIA MG-129 (MARIANA/MG)</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 10 - INSTRUMENTO A SER CRIADO - Fortalecimento dos Serviços de Inspeção Municipais</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 13 - 9445763 - OBRAS E SERVIÇOS PARA CONSTRUÇÃO E IMPLANTAÇÃO DE MELHORIAS RODOVIÁRIAS, OPERAÇÃO E MANUTENÇÃO DAS RODOVIAS DO LOTE OURO PRETO – MARIANA, COM PRIORIZAÇÃO DE DUPLICAÇÃO DA BR-356, DO ENTRONCAMENTO COM A BR-040 ATÉ O ENTRONCAMENTO COM A RODOVIA MG-129 (MARIANA/MG)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B22" t="n">
-        <v>1230</v>
+        <v>1320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
+          <t>SECRETARIA DE ESTADO DE SAÚDE - FES</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>3</v>
       </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
       <c r="F22" t="n">
-        <v>2371</v>
+        <v>4291</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE AGROPECUÁRIA - IMA</t>
+          <t>FUNDO ESTADUAL DE SAÚDE - FES</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J22" t="n">
-        <v>90</v>
+        <v>41</v>
       </c>
       <c r="K22" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L22" t="n">
         <v>80</v>
@@ -2928,102 +2699,90 @@
       <c r="M22" t="n">
         <v>1</v>
       </c>
-      <c r="N22" t="n">
-        <v>10521</v>
-      </c>
       <c r="O22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>609</v>
+        <v>301</v>
       </c>
       <c r="Q22" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="R22" t="n">
         <v>4</v>
       </c>
       <c r="S22" t="n">
-        <v>238</v>
+        <v>127</v>
       </c>
       <c r="T22" t="n">
-        <v>4238</v>
+        <v>4127</v>
       </c>
       <c r="U22" t="n">
         <v>1</v>
       </c>
-      <c r="V22" t="n">
-        <v>6874243</v>
-      </c>
-      <c r="W22" t="n">
-        <v>6874243</v>
-      </c>
       <c r="X22" t="n">
-        <v>6874243</v>
+        <v>14317500</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>REESTRUTURAÇÃO DO LABORATÓRIO DE QUÍMICA AGROPECUÁRIA DO INSTITUTO MINEIRO DE AGROPECUÁRIA.</t>
+          <t>ESTRUTURAÇÃO DA ATENÇÃO PRIMÁRIA</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>DEFESA SANITÁRIA</t>
+          <t>ATENÇÃO PRIMÁRIA À SAÚDE</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ANEXO 10</t>
+          <t>ANEXO 08</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>INSTRUMENTO A SER CRIADO</t>
+          <t>9445683</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>Reestruturação Do Laboratório De Química Agropecuária Do Instituto Mineiro De Agropecuária.</t>
+          <t>FORTALECIMENTO DO SISTEMA ÚNICO DE SAÚDE (SUS)</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 10 - INSTRUMENTO A SER CRIADO - Reestruturação Do Laboratório De Química Agropecuária Do Instituto Mineiro De Agropecuária.</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 08 - 9445683 - FORTALECIMENTO DO SISTEMA ÚNICO DE SAÚDE (SUS)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B23" t="n">
-        <v>1230</v>
+        <v>1370</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>3</v>
       </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
       <c r="F23" t="n">
-        <v>3041</v>
+        <v>1371</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>EMPRESA DE ASSISTÊNCIA TÉCNICA E EXTENSÃO RURAL DO ESTADO DE MINAS GERAIS - EMATER</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -3036,7 +2795,7 @@
         <v>90</v>
       </c>
       <c r="K23" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="L23" t="n">
         <v>80</v>
@@ -3044,55 +2803,46 @@
       <c r="M23" t="n">
         <v>1</v>
       </c>
-      <c r="N23" t="n">
-        <v>10518</v>
-      </c>
       <c r="O23" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P23" t="n">
-        <v>608</v>
+        <v>122</v>
       </c>
       <c r="Q23" t="n">
-        <v>97</v>
+        <v>705</v>
       </c>
       <c r="R23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>236</v>
+        <v>500</v>
       </c>
       <c r="T23" t="n">
-        <v>4236</v>
+        <v>2500</v>
       </c>
       <c r="U23" t="n">
         <v>1</v>
       </c>
-      <c r="V23" t="n">
-        <v>16000000</v>
-      </c>
-      <c r="W23" t="n">
-        <v>16000000</v>
-      </c>
       <c r="X23" t="n">
-        <v>16000000</v>
+        <v>12000000</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>FOMENTO PARA O DESENVOLVIMENTO DO SETOR AGROPECUÁRIO</t>
+          <t>ASSESSORAMENTO E GERENCIAMENTO DE POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>MINAS SEM FOME</t>
+          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3102,44 +2852,41 @@
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>INSTRUMENTO A SER CRIADO</t>
+          <t>9468057</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>Oferta de serviços de assistência técnica e extensão rural (metodologia ISA/PASEA), visando à produção de alimentos e estímulo à comercialização e adequação socioeconômica e ambiental de propriedades rurais</t>
+          <t>SUPORTE GERENCIAL, ADMINISTRATIVO, TECNOLÓGICO E DE COMUNICAÇÃO SOCIAL À IMPLEMENTAÇÃO DAS INICIATIVAS AMBIENTAIS</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Oferta de serviços de assistência técnica e extensão rural (metodologia ISA/PASEA), visando à produção de alimentos e estímulo à comercialização e adequação socioeconômica e ambiental de propriedades rurais</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9468057 - SUPORTE GERENCIAL, ADMINISTRATIVO, TECNOLÓGICO E DE COMUNICAÇÃO SOCIAL À IMPLEMENTAÇÃO DAS INICIATIVAS AMBIENTAIS</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B24" t="n">
-        <v>1230</v>
+        <v>1370</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUÁRIA E ABASTECIMENTO - SEAPA</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>3</v>
       </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
       <c r="F24" t="n">
-        <v>3041</v>
+        <v>1371</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>EMPRESA DE ASSISTÊNCIA TÉCNICA E EXTENSÃO RURAL DO ESTADO DE MINAS GERAIS - EMATER</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -3152,7 +2899,7 @@
         <v>90</v>
       </c>
       <c r="K24" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="L24" t="n">
         <v>80</v>
@@ -3160,55 +2907,46 @@
       <c r="M24" t="n">
         <v>1</v>
       </c>
-      <c r="N24" t="n">
-        <v>10518</v>
-      </c>
       <c r="O24" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P24" t="n">
-        <v>608</v>
+        <v>542</v>
       </c>
       <c r="Q24" t="n">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="R24" t="n">
         <v>4</v>
       </c>
       <c r="S24" t="n">
-        <v>236</v>
+        <v>38</v>
       </c>
       <c r="T24" t="n">
-        <v>4236</v>
+        <v>4038</v>
       </c>
       <c r="U24" t="n">
         <v>1</v>
       </c>
-      <c r="V24" t="n">
-        <v>24000000</v>
-      </c>
-      <c r="W24" t="n">
-        <v>24000000</v>
-      </c>
       <c r="X24" t="n">
-        <v>24000000</v>
+        <v>100000</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>FOMENTO PARA O DESENVOLVIMENTO DO SETOR AGROPECUÁRIO</t>
+          <t>FISCALIZAÇÃO AMBIENTAL</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>MINAS SEM FOME</t>
+          <t>MONITORAMENTO, CONTROLE E FISCALIZAÇÃO AMBIENTAL</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3218,158 +2956,145 @@
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>INSTRUMENTO A SER CRIADO</t>
+          <t>9456614</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>Oferta de serviços de assistência técnica e extensão rural (metodologia ISA/PASEA), visando à produção de alimentos e estímulo à comercialização e adequação socioeconômica e ambiental de propriedades rurais</t>
+          <t>AQUISIÇÃO DE MATERIAIS, EQUIPAMENTOS E CAPACITAÇÕES PARA MODERNIAÇÃO DAS ESTRUTURAS DE FISCALIZAÇÃO AMBIENTAL E SERVIÇOS DE INTELIGENCIA EM FISCALIZAÇÃO DA SECRETARIA ESTAUDAL DO MEIO AMBIENTEL DE MINAS GERAIS NA BACIA HIDROGRADICA DO RIO DOCE</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Oferta de serviços de assistência técnica e extensão rural (metodologia ISA/PASEA), visando à produção de alimentos e estímulo à comercialização e adequação socioeconômica e ambiental de propriedades rurais</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9456614 - AQUISIÇÃO DE MATERIAIS, EQUIPAMENTOS E CAPACITAÇÕES PARA MODERNIAÇÃO DAS ESTRUTURAS DE FISCALIZAÇÃO AMBIENTAL E SERVIÇOS DE INTELIGENCIA EM FISCALIZAÇÃO DA SECRETARIA ESTAUDAL DO MEIO AMBIENTEL DE MINAS GERAIS NA BACIA HIDROGRADICA DO RIO DOCE</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B25" t="n">
-        <v>1300</v>
+        <v>1370</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>3</v>
       </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
       <c r="F25" t="n">
-        <v>1301</v>
+        <v>1371</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS - SEINFRA</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J25" t="n">
         <v>90</v>
       </c>
       <c r="K25" t="n">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="L25" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M25" t="n">
         <v>1</v>
       </c>
-      <c r="N25" t="n">
-        <v>10659</v>
-      </c>
       <c r="O25" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="P25" t="n">
-        <v>130</v>
+        <v>542</v>
       </c>
       <c r="Q25" t="n">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="R25" t="n">
         <v>4</v>
       </c>
       <c r="S25" t="n">
-        <v>345</v>
+        <v>38</v>
       </c>
       <c r="T25" t="n">
-        <v>4345</v>
+        <v>4038</v>
       </c>
       <c r="U25" t="n">
         <v>1</v>
       </c>
-      <c r="V25" t="n">
-        <v>324155748</v>
-      </c>
-      <c r="W25" t="n">
-        <v>324155748</v>
-      </c>
       <c r="X25" t="n">
-        <v>324155748</v>
+        <v>900000</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>GESTÃO DO RODOANEL METROPOLITANO</t>
+          <t>FISCALIZAÇÃO AMBIENTAL</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>PROMOÇÃO DE CONCESSÕES E PARCERIAS</t>
+          <t>MONITORAMENTO, CONTROLE E FISCALIZAÇÃO AMBIENTAL</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Acordo Judicial Vale</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ANEXO III</t>
-        </is>
-      </c>
-      <c r="AD25" t="n">
-        <v>9288180</v>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>9456614</t>
+        </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>Implantação do Rodoanel da Região Metropolitana de Belo Horizonte</t>
+          <t>AQUISIÇÃO DE MATERIAIS, EQUIPAMENTOS E CAPACITAÇÕES PARA MODERNIAÇÃO DAS ESTRUTURAS DE FISCALIZAÇÃO AMBIENTAL E SERVIÇOS DE INTELIGENCIA EM FISCALIZAÇÃO DA SECRETARIA ESTAUDAL DO MEIO AMBIENTEL DE MINAS GERAIS NA BACIA HIDROGRADICA DO RIO DOCE</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>Acordo Judicial Vale - ANEXO III - 9288180 - Implantação do Rodoanel da Região Metropolitana de Belo Horizonte</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9456614 - AQUISIÇÃO DE MATERIAIS, EQUIPAMENTOS E CAPACITAÇÕES PARA MODERNIAÇÃO DAS ESTRUTURAS DE FISCALIZAÇÃO AMBIENTAL E SERVIÇOS DE INTELIGENCIA EM FISCALIZAÇÃO DA SECRETARIA ESTAUDAL DO MEIO AMBIENTEL DE MINAS GERAIS NA BACIA HIDROGRADICA DO RIO DOCE</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B26" t="n">
-        <v>1300</v>
+        <v>1370</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>3</v>
       </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
       <c r="F26" t="n">
-        <v>1301</v>
+        <v>1371</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS - SEINFRA</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -3382,108 +3107,98 @@
         <v>90</v>
       </c>
       <c r="K26" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L26" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M26" t="n">
         <v>1</v>
       </c>
-      <c r="N26" t="n">
-        <v>10552</v>
-      </c>
       <c r="O26" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P26" t="n">
-        <v>451</v>
+        <v>542</v>
       </c>
       <c r="Q26" t="n">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S26" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T26" t="n">
-        <v>1040</v>
+        <v>4038</v>
       </c>
       <c r="U26" t="n">
         <v>1</v>
       </c>
-      <c r="V26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1000</v>
-      </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>350000</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>REQUALIFICAÇÃO URBANA E AMBIENTAL E CONTROLE DE CHEIAS DO CÓRREGO FERRUGEM - PAC FERRUGEM (VALE)</t>
+          <t>FISCALIZAÇÃO AMBIENTAL</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>DESENVOLVIMENTO DA INFRAESTRUTURA ESTADUAL, MUNICIPAL E REGIONAL</t>
+          <t>MONITORAMENTO, CONTROLE E FISCALIZAÇÃO AMBIENTAL</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Acordo Judicial Vale</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ANEXO IV</t>
-        </is>
-      </c>
-      <c r="AD26" t="n">
-        <v>9288178</v>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>9456614</t>
+        </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>Prevenção de Enchentes - Construção de Bacias de Contenção no Córrego Ferrugem</t>
+          <t>AQUISIÇÃO DE MATERIAIS, EQUIPAMENTOS E CAPACITAÇÕES PARA MODERNIAÇÃO DAS ESTRUTURAS DE FISCALIZAÇÃO AMBIENTAL E SERVIÇOS DE INTELIGENCIA EM FISCALIZAÇÃO DA SECRETARIA ESTAUDAL DO MEIO AMBIENTEL DE MINAS GERAIS NA BACIA HIDROGRADICA DO RIO DOCE</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>Acordo Judicial Vale - ANEXO IV - 9288178 - Prevenção de Enchentes - Construção de Bacias de Contenção no Córrego Ferrugem</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9456614 - AQUISIÇÃO DE MATERIAIS, EQUIPAMENTOS E CAPACITAÇÕES PARA MODERNIAÇÃO DAS ESTRUTURAS DE FISCALIZAÇÃO AMBIENTAL E SERVIÇOS DE INTELIGENCIA EM FISCALIZAÇÃO DA SECRETARIA ESTAUDAL DO MEIO AMBIENTEL DE MINAS GERAIS NA BACIA HIDROGRADICA DO RIO DOCE</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B27" t="n">
-        <v>1300</v>
+        <v>1370</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>3</v>
       </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
       <c r="F27" t="n">
-        <v>1301</v>
+        <v>1371</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS - SEINFRA</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -3496,108 +3211,98 @@
         <v>90</v>
       </c>
       <c r="K27" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="L27" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" t="n">
-        <v>10554</v>
-      </c>
       <c r="O27" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P27" t="n">
-        <v>451</v>
+        <v>542</v>
       </c>
       <c r="Q27" t="n">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S27" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="T27" t="n">
-        <v>1042</v>
+        <v>4038</v>
       </c>
       <c r="U27" t="n">
         <v>1</v>
       </c>
-      <c r="V27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1000</v>
-      </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>1150000</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>REQUALIFICAÇÃO URBANA E AMBIENTAL E DE CONTROLE DE CHEIAS DO CÓRREGO RIACHO DAS PEDRAS (VALE)</t>
+          <t>FISCALIZAÇÃO AMBIENTAL</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>DESENVOLVIMENTO DA INFRAESTRUTURA ESTADUAL, MUNICIPAL E REGIONAL</t>
+          <t>MONITORAMENTO, CONTROLE E FISCALIZAÇÃO AMBIENTAL</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Acordo Judicial Vale</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ANEXO IV</t>
-        </is>
-      </c>
-      <c r="AD27" t="n">
-        <v>9288179</v>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>9456614</t>
+        </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>Prevenção de Enchentes - Desapropriação para construção de bacias de contenção no Córrego Riacho das Pedras</t>
+          <t>AQUISIÇÃO DE MATERIAIS, EQUIPAMENTOS E CAPACITAÇÕES PARA MODERNIAÇÃO DAS ESTRUTURAS DE FISCALIZAÇÃO AMBIENTAL E SERVIÇOS DE INTELIGENCIA EM FISCALIZAÇÃO DA SECRETARIA ESTAUDAL DO MEIO AMBIENTEL DE MINAS GERAIS NA BACIA HIDROGRADICA DO RIO DOCE</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>Acordo Judicial Vale - ANEXO IV - 9288179 - Prevenção de Enchentes - Desapropriação para construção de bacias de contenção no Córrego Riacho das Pedras</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9456614 - AQUISIÇÃO DE MATERIAIS, EQUIPAMENTOS E CAPACITAÇÕES PARA MODERNIAÇÃO DAS ESTRUTURAS DE FISCALIZAÇÃO AMBIENTAL E SERVIÇOS DE INTELIGENCIA EM FISCALIZAÇÃO DA SECRETARIA ESTAUDAL DO MEIO AMBIENTEL DE MINAS GERAIS NA BACIA HIDROGRADICA DO RIO DOCE</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B28" t="n">
-        <v>1300</v>
+        <v>1370</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>3</v>
       </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
       <c r="F28" t="n">
-        <v>2301</v>
+        <v>1371</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS - DER-MG</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -3610,7 +3315,7 @@
         <v>90</v>
       </c>
       <c r="K28" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="L28" t="n">
         <v>80</v>
@@ -3618,55 +3323,46 @@
       <c r="M28" t="n">
         <v>1</v>
       </c>
-      <c r="N28" t="n">
-        <v>10559</v>
-      </c>
       <c r="O28" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="P28" t="n">
-        <v>782</v>
+        <v>542</v>
       </c>
       <c r="Q28" t="n">
-        <v>81</v>
+        <v>705</v>
       </c>
       <c r="R28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
-        <v>268</v>
+        <v>74</v>
       </c>
       <c r="T28" t="n">
-        <v>4268</v>
+        <v>1074</v>
       </c>
       <c r="U28" t="n">
         <v>1</v>
       </c>
-      <c r="V28" t="n">
-        <v>41300000</v>
-      </c>
-      <c r="W28" t="n">
-        <v>41300000</v>
-      </c>
       <c r="X28" t="n">
-        <v>41300000</v>
+        <v>6600000</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>AMPLIAÇÃO DE CAPACIDADE DA MALHA E RESTAURAÇÃO DO PAVIMENTO</t>
+          <t>TRANSFORMAÇÃO DIGITAL DO SISEMA</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>DESENVOLVIMENTO SUSTENTÁVEL DA INFRAESTRUTURA RODOVIÁRIA</t>
+          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3674,57 +3370,56 @@
           <t>ANEXO 12</t>
         </is>
       </c>
-      <c r="AD28" t="n">
-        <v>9452379</v>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>9480692</t>
+        </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>Ampliação e melhoria na pavimentação, manutenção e recuperação funcional da infraestrutura viária</t>
+          <t xml:space="preserve">Desenvolvimento e manutenção de sistemas de tecnologia e informação do Sistema Estadual do Meio Ambiente (SISEMA) de forma a apoiar os investimentos ambientais na Bacia Hidrográfica do Rio Doce. </t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9452379 - Ampliação e melhoria na pavimentação, manutenção e recuperação funcional da infraestrutura viária</t>
+          <t xml:space="preserve">ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9480692 - Desenvolvimento e manutenção de sistemas de tecnologia e informação do Sistema Estadual do Meio Ambiente (SISEMA) de forma a apoiar os investimentos ambientais na Bacia Hidrográfica do Rio Doce. </t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B29" t="n">
-        <v>1300</v>
+        <v>1370</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>3</v>
       </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
       <c r="F29" t="n">
-        <v>2301</v>
+        <v>2101</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS - DER-MG</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J29" t="n">
         <v>90</v>
       </c>
       <c r="K29" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="L29" t="n">
         <v>80</v>
@@ -3732,55 +3427,46 @@
       <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="N29" t="n">
-        <v>10568</v>
-      </c>
       <c r="O29" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="P29" t="n">
-        <v>782</v>
+        <v>541</v>
       </c>
       <c r="Q29" t="n">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="R29" t="n">
         <v>4</v>
       </c>
       <c r="S29" t="n">
-        <v>275</v>
+        <v>54</v>
       </c>
       <c r="T29" t="n">
-        <v>4275</v>
+        <v>4054</v>
       </c>
       <c r="U29" t="n">
         <v>1</v>
       </c>
-      <c r="V29" t="n">
-        <v>115000000</v>
-      </c>
-      <c r="W29" t="n">
-        <v>115000000</v>
-      </c>
       <c r="X29" t="n">
-        <v>115000000</v>
+        <v>990000</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>IMPLANTAÇÃO/PAVIMENTAÇÃO DA MALHA</t>
+          <t>PREVENÇÃO E COMBATE A INCÊNDIOS FLORESTAIS</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>DESENVOLVIMENTO SUSTENTÁVEL DA INFRAESTRUTURA RODOVIÁRIA</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3788,158 +3474,147 @@
           <t>ANEXO 12</t>
         </is>
       </c>
-      <c r="AD29" t="n">
-        <v>9452379</v>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>9456606</t>
+        </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>Ampliação e melhoria na pavimentação, manutenção e recuperação funcional da infraestrutura viária</t>
+          <t xml:space="preserve">CONSOLIDAÇÃO DE UNIDADES DE CONSERVAÇÃO ESTADUAIS NA BACIA HIDROGRÁFICA DO RIO DOCE, A PARTIR DO INVESTIMENTO E CUSTEIO DE SUAS ESTRUTURAS E SERVIÇOS PRESTADOS, DE ACORDO COM SEUS OBJETIVOS DE CRIAÇÃO; CRIAÇÃO, SE NECESSÁRIO, DE NOVA(S) UNIDADE(S) DE CONSERVAÇÃO NA BACIA HIDROGRÁFICA DO RIO DOCE DE ACORDO COM MAPEAMENTO DE ÁREAS PRIORITÁRIAS PARA CONSERVAÇÃO; REALIZAÇÃO DE ATIVIDADES DE PREVENÇÃO E COMBATE A INCÊNDIOS E REGULARIZAÇÃO FUNDIÁRIA DAS UNIDADES DE CONSERVAÇÃO </t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9452379 - Ampliação e melhoria na pavimentação, manutenção e recuperação funcional da infraestrutura viária</t>
+          <t xml:space="preserve">ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9456606 - CONSOLIDAÇÃO DE UNIDADES DE CONSERVAÇÃO ESTADUAIS NA BACIA HIDROGRÁFICA DO RIO DOCE, A PARTIR DO INVESTIMENTO E CUSTEIO DE SUAS ESTRUTURAS E SERVIÇOS PRESTADOS, DE ACORDO COM SEUS OBJETIVOS DE CRIAÇÃO; CRIAÇÃO, SE NECESSÁRIO, DE NOVA(S) UNIDADE(S) DE CONSERVAÇÃO NA BACIA HIDROGRÁFICA DO RIO DOCE DE ACORDO COM MAPEAMENTO DE ÁREAS PRIORITÁRIAS PARA CONSERVAÇÃO; REALIZAÇÃO DE ATIVIDADES DE PREVENÇÃO E COMBATE A INCÊNDIOS E REGULARIZAÇÃO FUNDIÁRIA DAS UNIDADES DE CONSERVAÇÃO </t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B30" t="n">
-        <v>1300</v>
+        <v>1370</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>3</v>
       </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
       <c r="F30" t="n">
-        <v>2301</v>
+        <v>2101</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS - DER-MG</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J30" t="n">
         <v>90</v>
       </c>
       <c r="K30" t="n">
-        <v>93</v>
+        <v>40</v>
       </c>
       <c r="L30" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M30" t="n">
         <v>1</v>
       </c>
-      <c r="N30" t="n">
-        <v>10582</v>
-      </c>
       <c r="O30" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="P30" t="n">
-        <v>782</v>
+        <v>541</v>
       </c>
       <c r="Q30" t="n">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="R30" t="n">
         <v>4</v>
       </c>
       <c r="S30" t="n">
-        <v>287</v>
+        <v>54</v>
       </c>
       <c r="T30" t="n">
-        <v>4287</v>
+        <v>4054</v>
       </c>
       <c r="U30" t="n">
         <v>1</v>
       </c>
-      <c r="V30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1000</v>
-      </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>CONSTRUÇÃO E ADEQUAÇÃO DE RODOVIAS - RIO DOCE</t>
+          <t>PREVENÇÃO E COMBATE A INCÊNDIOS FLORESTAIS</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>DESENVOLVIMENTO SUSTENTÁVEL DA INFRAESTRUTURA RODOVIÁRIA</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Agenda Integrada - Renova</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Sem anexo</t>
-        </is>
-      </c>
-      <c r="AD30" t="n">
-        <v>9382040</v>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>9456606</t>
+        </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>Marliéria</t>
+          <t xml:space="preserve">CONSOLIDAÇÃO DE UNIDADES DE CONSERVAÇÃO ESTADUAIS NA BACIA HIDROGRÁFICA DO RIO DOCE, A PARTIR DO INVESTIMENTO E CUSTEIO DE SUAS ESTRUTURAS E SERVIÇOS PRESTADOS, DE ACORDO COM SEUS OBJETIVOS DE CRIAÇÃO; CRIAÇÃO, SE NECESSÁRIO, DE NOVA(S) UNIDADE(S) DE CONSERVAÇÃO NA BACIA HIDROGRÁFICA DO RIO DOCE DE ACORDO COM MAPEAMENTO DE ÁREAS PRIORITÁRIAS PARA CONSERVAÇÃO; REALIZAÇÃO DE ATIVIDADES DE PREVENÇÃO E COMBATE A INCÊNDIOS E REGULARIZAÇÃO FUNDIÁRIA DAS UNIDADES DE CONSERVAÇÃO </t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>Agenda Integrada - Renova - Sem anexo - 9382040 - Marliéria</t>
+          <t xml:space="preserve">ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9456606 - CONSOLIDAÇÃO DE UNIDADES DE CONSERVAÇÃO ESTADUAIS NA BACIA HIDROGRÁFICA DO RIO DOCE, A PARTIR DO INVESTIMENTO E CUSTEIO DE SUAS ESTRUTURAS E SERVIÇOS PRESTADOS, DE ACORDO COM SEUS OBJETIVOS DE CRIAÇÃO; CRIAÇÃO, SE NECESSÁRIO, DE NOVA(S) UNIDADE(S) DE CONSERVAÇÃO NA BACIA HIDROGRÁFICA DO RIO DOCE DE ACORDO COM MAPEAMENTO DE ÁREAS PRIORITÁRIAS PARA CONSERVAÇÃO; REALIZAÇÃO DE ATIVIDADES DE PREVENÇÃO E COMBATE A INCÊNDIOS E REGULARIZAÇÃO FUNDIÁRIA DAS UNIDADES DE CONSERVAÇÃO </t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B31" t="n">
-        <v>1300</v>
+        <v>1370</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>3</v>
       </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
       <c r="F31" t="n">
-        <v>2301</v>
+        <v>2101</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS - DER-MG</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -3952,108 +3627,98 @@
         <v>90</v>
       </c>
       <c r="K31" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="L31" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" t="n">
-        <v>10584</v>
-      </c>
       <c r="O31" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="P31" t="n">
-        <v>782</v>
+        <v>541</v>
       </c>
       <c r="Q31" t="n">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="R31" t="n">
         <v>4</v>
       </c>
       <c r="S31" t="n">
-        <v>289</v>
+        <v>54</v>
       </c>
       <c r="T31" t="n">
-        <v>4289</v>
+        <v>4054</v>
       </c>
       <c r="U31" t="n">
         <v>1</v>
       </c>
-      <c r="V31" t="n">
-        <v>99517258</v>
-      </c>
-      <c r="W31" t="n">
-        <v>99517258</v>
-      </c>
       <c r="X31" t="n">
-        <v>99517258</v>
+        <v>200000</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>CONSTRUÇÃO E ADEQUAÇÃO DE RODOVIAS - RECUPERAÇÃO BRUMADINHO</t>
+          <t>PREVENÇÃO E COMBATE A INCÊNDIOS FLORESTAIS</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>DESENVOLVIMENTO SUSTENTÁVEL DA INFRAESTRUTURA RODOVIÁRIA</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Acordo Judicial Vale</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ANEXO III</t>
-        </is>
-      </c>
-      <c r="AD31" t="n">
-        <v>9288132</v>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>9456606</t>
+        </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>Construção de pontes em São Francisco, Manga e São Romão sobre o Rio São Francisco</t>
+          <t xml:space="preserve">CONSOLIDAÇÃO DE UNIDADES DE CONSERVAÇÃO ESTADUAIS NA BACIA HIDROGRÁFICA DO RIO DOCE, A PARTIR DO INVESTIMENTO E CUSTEIO DE SUAS ESTRUTURAS E SERVIÇOS PRESTADOS, DE ACORDO COM SEUS OBJETIVOS DE CRIAÇÃO; CRIAÇÃO, SE NECESSÁRIO, DE NOVA(S) UNIDADE(S) DE CONSERVAÇÃO NA BACIA HIDROGRÁFICA DO RIO DOCE DE ACORDO COM MAPEAMENTO DE ÁREAS PRIORITÁRIAS PARA CONSERVAÇÃO; REALIZAÇÃO DE ATIVIDADES DE PREVENÇÃO E COMBATE A INCÊNDIOS E REGULARIZAÇÃO FUNDIÁRIA DAS UNIDADES DE CONSERVAÇÃO </t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>Acordo Judicial Vale - ANEXO III - 9288132 - Construção de pontes em São Francisco, Manga e São Romão sobre o Rio São Francisco</t>
+          <t xml:space="preserve">ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9456606 - CONSOLIDAÇÃO DE UNIDADES DE CONSERVAÇÃO ESTADUAIS NA BACIA HIDROGRÁFICA DO RIO DOCE, A PARTIR DO INVESTIMENTO E CUSTEIO DE SUAS ESTRUTURAS E SERVIÇOS PRESTADOS, DE ACORDO COM SEUS OBJETIVOS DE CRIAÇÃO; CRIAÇÃO, SE NECESSÁRIO, DE NOVA(S) UNIDADE(S) DE CONSERVAÇÃO NA BACIA HIDROGRÁFICA DO RIO DOCE DE ACORDO COM MAPEAMENTO DE ÁREAS PRIORITÁRIAS PARA CONSERVAÇÃO; REALIZAÇÃO DE ATIVIDADES DE PREVENÇÃO E COMBATE A INCÊNDIOS E REGULARIZAÇÃO FUNDIÁRIA DAS UNIDADES DE CONSERVAÇÃO </t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B32" t="n">
-        <v>1300</v>
+        <v>1370</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>3</v>
       </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
       <c r="F32" t="n">
-        <v>2301</v>
+        <v>2101</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS - DER-MG</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -4066,121 +3731,111 @@
         <v>90</v>
       </c>
       <c r="K32" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L32" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M32" t="n">
         <v>1</v>
       </c>
-      <c r="N32" t="n">
-        <v>10584</v>
-      </c>
       <c r="O32" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="P32" t="n">
-        <v>782</v>
+        <v>541</v>
       </c>
       <c r="Q32" t="n">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="R32" t="n">
         <v>4</v>
       </c>
       <c r="S32" t="n">
-        <v>289</v>
+        <v>54</v>
       </c>
       <c r="T32" t="n">
-        <v>4289</v>
+        <v>4054</v>
       </c>
       <c r="U32" t="n">
         <v>1</v>
       </c>
-      <c r="V32" t="n">
-        <v>158250000</v>
-      </c>
-      <c r="W32" t="n">
-        <v>158250000</v>
-      </c>
       <c r="X32" t="n">
-        <v>158250000</v>
+        <v>3800000</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>CONSTRUÇÃO E ADEQUAÇÃO DE RODOVIAS - RECUPERAÇÃO BRUMADINHO</t>
+          <t>PREVENÇÃO E COMBATE A INCÊNDIOS FLORESTAIS</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>DESENVOLVIMENTO SUSTENTÁVEL DA INFRAESTRUTURA RODOVIÁRIA</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Acordo Judicial Vale</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ANEXO III</t>
-        </is>
-      </c>
-      <c r="AD32" t="n">
-        <v>9288133</v>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>9456606</t>
+        </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>Recuperação de rodovias pavimentadas em pior estado, conforme avaliação técnica do DER-MG/conclusão de corredor logístico estruturante, conforme critérios técnicos da SEINFRA</t>
+          <t xml:space="preserve">CONSOLIDAÇÃO DE UNIDADES DE CONSERVAÇÃO ESTADUAIS NA BACIA HIDROGRÁFICA DO RIO DOCE, A PARTIR DO INVESTIMENTO E CUSTEIO DE SUAS ESTRUTURAS E SERVIÇOS PRESTADOS, DE ACORDO COM SEUS OBJETIVOS DE CRIAÇÃO; CRIAÇÃO, SE NECESSÁRIO, DE NOVA(S) UNIDADE(S) DE CONSERVAÇÃO NA BACIA HIDROGRÁFICA DO RIO DOCE DE ACORDO COM MAPEAMENTO DE ÁREAS PRIORITÁRIAS PARA CONSERVAÇÃO; REALIZAÇÃO DE ATIVIDADES DE PREVENÇÃO E COMBATE A INCÊNDIOS E REGULARIZAÇÃO FUNDIÁRIA DAS UNIDADES DE CONSERVAÇÃO </t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>Acordo Judicial Vale - ANEXO III - 9288133 - Recuperação de rodovias pavimentadas em pior estado, conforme avaliação técnica do DER-MG/conclusão de corredor logístico estruturante, conforme critérios técnicos da SEINFRA</t>
+          <t xml:space="preserve">ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9456606 - CONSOLIDAÇÃO DE UNIDADES DE CONSERVAÇÃO ESTADUAIS NA BACIA HIDROGRÁFICA DO RIO DOCE, A PARTIR DO INVESTIMENTO E CUSTEIO DE SUAS ESTRUTURAS E SERVIÇOS PRESTADOS, DE ACORDO COM SEUS OBJETIVOS DE CRIAÇÃO; CRIAÇÃO, SE NECESSÁRIO, DE NOVA(S) UNIDADE(S) DE CONSERVAÇÃO NA BACIA HIDROGRÁFICA DO RIO DOCE DE ACORDO COM MAPEAMENTO DE ÁREAS PRIORITÁRIAS PARA CONSERVAÇÃO; REALIZAÇÃO DE ATIVIDADES DE PREVENÇÃO E COMBATE A INCÊNDIOS E REGULARIZAÇÃO FUNDIÁRIA DAS UNIDADES DE CONSERVAÇÃO </t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B33" t="n">
-        <v>1300</v>
+        <v>1370</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>3</v>
       </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
       <c r="F33" t="n">
-        <v>2301</v>
+        <v>2101</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS - DER-MG</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J33" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="K33" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="L33" t="n">
         <v>80</v>
@@ -4188,113 +3843,103 @@
       <c r="M33" t="n">
         <v>1</v>
       </c>
-      <c r="N33" t="n">
-        <v>10589</v>
-      </c>
       <c r="O33" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="P33" t="n">
-        <v>782</v>
+        <v>541</v>
       </c>
       <c r="Q33" t="n">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="R33" t="n">
         <v>4</v>
       </c>
       <c r="S33" t="n">
-        <v>293</v>
+        <v>58</v>
       </c>
       <c r="T33" t="n">
-        <v>4293</v>
+        <v>4058</v>
       </c>
       <c r="U33" t="n">
         <v>1</v>
       </c>
-      <c r="V33" t="n">
-        <v>53897833</v>
-      </c>
-      <c r="W33" t="n">
-        <v>53897833</v>
-      </c>
       <c r="X33" t="n">
-        <v>53897833</v>
+        <v>12250000</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>CONSERVAÇÃO ROTINEIRA DA MALHA VIÁRIA</t>
+          <t>PROTEÇÃO E CONSERVAÇÃO DA FAUNA SILVESTRE</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>DESENVOLVIMENTO SUSTENTÁVEL DA INFRAESTRUTURA RODOVIÁRIA</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>ANEXO 12</t>
-        </is>
-      </c>
-      <c r="AD33" t="n">
-        <v>9452379</v>
+          <t>ANEXO 10</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>9480691</t>
+        </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>Ampliação e melhoria na pavimentação, manutenção e recuperação funcional da infraestrutura viária</t>
+          <t>ELABORAÇÃO E/OU ATUALIZAÇÃO DO ORDENAMENTO PESQUEIRO, NA FORMA DA LEI N. 11.959, DE 29 DE JUNHO DE 2009. III. RECOMPOSIÇÃO DA BIOTA, DOS RECURSOS E DOS ESTOQUES PESQUEIROS DO ECOSSISTEMA COMO UM TODO NA BACIA HIDROGRÁFICA DO RIO DOCE, EM SUA FOZ E REGIÃO COSTEIRA E MARINHA.</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9452379 - Ampliação e melhoria na pavimentação, manutenção e recuperação funcional da infraestrutura viária</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 10 - 9480691 - ELABORAÇÃO E/OU ATUALIZAÇÃO DO ORDENAMENTO PESQUEIRO, NA FORMA DA LEI N. 11.959, DE 29 DE JUNHO DE 2009. III. RECOMPOSIÇÃO DA BIOTA, DOS RECURSOS E DOS ESTOQUES PESQUEIROS DO ECOSSISTEMA COMO UM TODO NA BACIA HIDROGRÁFICA DO RIO DOCE, EM SUA FOZ E REGIÃO COSTEIRA E MARINHA.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B34" t="n">
-        <v>1300</v>
+        <v>1370</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D34" t="n">
         <v>3</v>
       </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
       <c r="F34" t="n">
-        <v>2301</v>
+        <v>2101</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS - DER-MG</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J34" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="K34" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="L34" t="n">
         <v>80</v>
@@ -4302,55 +3947,46 @@
       <c r="M34" t="n">
         <v>1</v>
       </c>
-      <c r="N34" t="n">
-        <v>10722</v>
-      </c>
       <c r="O34" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="P34" t="n">
-        <v>782</v>
+        <v>541</v>
       </c>
       <c r="Q34" t="n">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="R34" t="n">
         <v>4</v>
       </c>
       <c r="S34" t="n">
-        <v>385</v>
+        <v>58</v>
       </c>
       <c r="T34" t="n">
-        <v>4385</v>
+        <v>4058</v>
       </c>
       <c r="U34" t="n">
         <v>1</v>
       </c>
-      <c r="V34" t="n">
-        <v>54435022</v>
-      </c>
-      <c r="W34" t="n">
-        <v>54435022</v>
-      </c>
       <c r="X34" t="n">
-        <v>54435022</v>
+        <v>3500000</v>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>REABILITAÇÃO DA MALHA VIÁRIA</t>
+          <t>PROTEÇÃO E CONSERVAÇÃO DA FAUNA SILVESTRE</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>DESENVOLVIMENTO SUSTENTÁVEL DA INFRAESTRUTURA RODOVIÁRIA</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4358,57 +3994,56 @@
           <t>ANEXO 12</t>
         </is>
       </c>
-      <c r="AD34" t="n">
-        <v>9452379</v>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>9456612</t>
+        </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>Ampliação e melhoria na pavimentação, manutenção e recuperação funcional da infraestrutura viária</t>
+          <t>REVITALIZAÇÃO AQUÁTICA DA BACIA HIDROGRÁFICA DO RIO DOCE, A PARTIR DO MAPEAMENTO DE ÁREAS ESTRATÉGICAS PARA REVITALIZAÇÃO E CONSERVAÇÃO DA FAUNA E FLORA AQUÁTICAS, EM ESPECIAL ÁREAS DE CABECEIRAS, TRIBUTÁRIOS E ROTAS DE PIRACEMA, E EXECUÇÃO DE AÇÕES COMO ZONEAMENTO PESQUEIRO; DESASSOREAMENTO; RECONFORMAÇÃO DE CALHAS DE RIOS; RENATURALIZAÇÃO DE LEITOS DE RIOS; REINTRODUÇÃO DE ESPÉCIES AQUÁTICAS AMEAÇADAS;</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9452379 - Ampliação e melhoria na pavimentação, manutenção e recuperação funcional da infraestrutura viária</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9456612 - REVITALIZAÇÃO AQUÁTICA DA BACIA HIDROGRÁFICA DO RIO DOCE, A PARTIR DO MAPEAMENTO DE ÁREAS ESTRATÉGICAS PARA REVITALIZAÇÃO E CONSERVAÇÃO DA FAUNA E FLORA AQUÁTICAS, EM ESPECIAL ÁREAS DE CABECEIRAS, TRIBUTÁRIOS E ROTAS DE PIRACEMA, E EXECUÇÃO DE AÇÕES COMO ZONEAMENTO PESQUEIRO; DESASSOREAMENTO; RECONFORMAÇÃO DE CALHAS DE RIOS; RENATURALIZAÇÃO DE LEITOS DE RIOS; REINTRODUÇÃO DE ESPÉCIES AQUÁTICAS AMEAÇADAS;</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B35" t="n">
-        <v>1300</v>
+        <v>1370</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D35" t="n">
         <v>3</v>
       </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
       <c r="F35" t="n">
-        <v>4631</v>
+        <v>2101</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>FUNDO DE PAGAMENTO DE PARCERIAS PÚBLICO - PRIVADAS DE MINAS GERAIS - FPP - MG</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J35" t="n">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="K35" t="n">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="L35" t="n">
         <v>80</v>
@@ -4416,214 +4051,194 @@
       <c r="M35" t="n">
         <v>1</v>
       </c>
-      <c r="N35" t="n">
-        <v>11043</v>
-      </c>
       <c r="O35" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="P35" t="n">
-        <v>130</v>
+        <v>541</v>
       </c>
       <c r="Q35" t="n">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="R35" t="n">
         <v>4</v>
       </c>
       <c r="S35" t="n">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="T35" t="n">
-        <v>4128</v>
+        <v>4058</v>
       </c>
       <c r="U35" t="n">
         <v>1</v>
       </c>
-      <c r="V35" t="n">
-        <v>345000000</v>
-      </c>
-      <c r="W35" t="n">
-        <v>345000000</v>
-      </c>
       <c r="X35" t="n">
-        <v>345000000</v>
+        <v>500000</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>LOTE OURO PRETO</t>
+          <t>PROTEÇÃO E CONSERVAÇÃO DA FAUNA SILVESTRE</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>PROMOÇÃO DE CONCESSÕES E PARCERIAS</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>ANEXO 13</t>
-        </is>
-      </c>
-      <c r="AD35" t="n">
-        <v>9445763</v>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>9456605</t>
+        </is>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>Obras e serviços para construção e implantação de melhorias rodoviárias, operação e manutenção das rodovias do lote Ouro Preto – Mariana, com priorização de duplicação da BR-356, do entroncamento com a BR-040 até o entroncamento com a Rodovia MG-129 (Mariana/MG)</t>
+          <t>FORTALECIMENTO DA POLÍTICA PÚBLICA DE GESTÃO DO MANEJO DA FAUNA SILVESTRE, DE ACORDO COM MAPEAMENTO DE NECESSIDADES A SER DETALHADO, A PARTIR DE AÇÕES COMO DA ESTRUTURAÇÃO E CUSTEIO DOS SERVIÇOS PRESTADOS PELOS CETRAS QUE ATENDAM À BACIA HIDROGRÁFICA DO RIO DOCE; CONTRATAÇÃO DE SERVIÇOS VETERINÁRIOS ESPECIALIZADOS; CONSTRUÇÃO DE VIVEIROS EM ÁREAS DE PARCEIROS PARA A REABILITAÇÃO E CONSERVAÇÃO DA FAUNA</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 13 - 9445763 - Obras e serviços para construção e implantação de melhorias rodoviárias, operação e manutenção das rodovias do lote Ouro Preto – Mariana, com priorização de duplicação da BR-356, do entroncamento com a BR-040 até o entroncamento com a Rodovia MG-129 (Mariana/MG)</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9456605 - FORTALECIMENTO DA POLÍTICA PÚBLICA DE GESTÃO DO MANEJO DA FAUNA SILVESTRE, DE ACORDO COM MAPEAMENTO DE NECESSIDADES A SER DETALHADO, A PARTIR DE AÇÕES COMO DA ESTRUTURAÇÃO E CUSTEIO DOS SERVIÇOS PRESTADOS PELOS CETRAS QUE ATENDAM À BACIA HIDROGRÁFICA DO RIO DOCE; CONTRATAÇÃO DE SERVIÇOS VETERINÁRIOS ESPECIALIZADOS; CONSTRUÇÃO DE VIVEIROS EM ÁREAS DE PARCEIROS PARA A REABILITAÇÃO E CONSERVAÇÃO DA FAUNA</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B36" t="n">
-        <v>1300</v>
+        <v>1370</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>3</v>
       </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
       <c r="F36" t="n">
-        <v>4631</v>
+        <v>2101</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>FUNDO DE PAGAMENTO DE PARCERIAS PÚBLICO - PRIVADAS DE MINAS GERAIS - FPP - MG</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H36" t="n">
         <v>4</v>
       </c>
       <c r="I36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J36" t="n">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="K36" t="n">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="L36" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="M36" t="n">
         <v>1</v>
       </c>
-      <c r="N36" t="n">
-        <v>10500</v>
-      </c>
       <c r="O36" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="P36" t="n">
-        <v>130</v>
+        <v>541</v>
       </c>
       <c r="Q36" t="n">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="R36" t="n">
         <v>4</v>
       </c>
       <c r="S36" t="n">
-        <v>220</v>
+        <v>58</v>
       </c>
       <c r="T36" t="n">
-        <v>4220</v>
+        <v>4058</v>
       </c>
       <c r="U36" t="n">
         <v>1</v>
       </c>
-      <c r="V36" t="n">
-        <v>500842252</v>
-      </c>
-      <c r="W36" t="n">
-        <v>500842252</v>
-      </c>
       <c r="X36" t="n">
-        <v>500842252</v>
+        <v>350000</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>RODOANEL METROPOLITANO DE BELO HORIZONTE</t>
+          <t>PROTEÇÃO E CONSERVAÇÃO DA FAUNA SILVESTRE</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>PROMOÇÃO DE CONCESSÕES E PARCERIAS</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Acordo Judicial Vale</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>ANEXO III</t>
-        </is>
-      </c>
-      <c r="AD36" t="n">
-        <v>9288180</v>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>9456605</t>
+        </is>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>Implantação do Rodoanel da Região Metropolitana de Belo Horizonte</t>
+          <t>FORTALECIMENTO DA POLÍTICA PÚBLICA DE GESTÃO DO MANEJO DA FAUNA SILVESTRE, DE ACORDO COM MAPEAMENTO DE NECESSIDADES A SER DETALHADO, A PARTIR DE AÇÕES COMO DA ESTRUTURAÇÃO E CUSTEIO DOS SERVIÇOS PRESTADOS PELOS CETRAS QUE ATENDAM À BACIA HIDROGRÁFICA DO RIO DOCE; CONTRATAÇÃO DE SERVIÇOS VETERINÁRIOS ESPECIALIZADOS; CONSTRUÇÃO DE VIVEIROS EM ÁREAS DE PARCEIROS PARA A REABILITAÇÃO E CONSERVAÇÃO DA FAUNA</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>Acordo Judicial Vale - ANEXO III - 9288180 - Implantação do Rodoanel da Região Metropolitana de Belo Horizonte</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9456605 - FORTALECIMENTO DA POLÍTICA PÚBLICA DE GESTÃO DO MANEJO DA FAUNA SILVESTRE, DE ACORDO COM MAPEAMENTO DE NECESSIDADES A SER DETALHADO, A PARTIR DE AÇÕES COMO DA ESTRUTURAÇÃO E CUSTEIO DOS SERVIÇOS PRESTADOS PELOS CETRAS QUE ATENDAM À BACIA HIDROGRÁFICA DO RIO DOCE; CONTRATAÇÃO DE SERVIÇOS VETERINÁRIOS ESPECIALIZADOS; CONSTRUÇÃO DE VIVEIROS EM ÁREAS DE PARCEIROS PARA A REABILITAÇÃO E CONSERVAÇÃO DA FAUNA</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B37" t="n">
-        <v>1320</v>
+        <v>1370</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE SAÚDE - SES</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D37" t="n">
         <v>3</v>
       </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
       <c r="F37" t="n">
-        <v>4291</v>
+        <v>2101</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SAÚDE - FES</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -4633,10 +4248,10 @@
         <v>4</v>
       </c>
       <c r="J37" t="n">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="K37" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L37" t="n">
         <v>80</v>
@@ -4644,100 +4259,90 @@
       <c r="M37" t="n">
         <v>1</v>
       </c>
-      <c r="N37" t="n">
-        <v>10380</v>
-      </c>
       <c r="O37" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="P37" t="n">
-        <v>302</v>
+        <v>541</v>
       </c>
       <c r="Q37" t="n">
+        <v>31</v>
+      </c>
+      <c r="R37" t="n">
+        <v>4</v>
+      </c>
+      <c r="S37" t="n">
         <v>58</v>
       </c>
-      <c r="R37" t="n">
-        <v>4</v>
-      </c>
-      <c r="S37" t="n">
-        <v>123</v>
-      </c>
       <c r="T37" t="n">
-        <v>4123</v>
+        <v>4058</v>
       </c>
       <c r="U37" t="n">
         <v>1</v>
       </c>
-      <c r="V37" t="n">
-        <v>76757500</v>
-      </c>
-      <c r="W37" t="n">
-        <v>76757500</v>
-      </c>
       <c r="X37" t="n">
-        <v>76757500</v>
+        <v>150000</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>ESTRUTURAÇÃO DA ATENÇÃO HOSPITALAR E DE URGÊNCIA E EMERGÊNCIA</t>
+          <t>PROTEÇÃO E CONSERVAÇÃO DA FAUNA SILVESTRE</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>POLÍTICAS DE ATENÇÃO HOSPITALAR</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>ANEXO 08</t>
-        </is>
-      </c>
-      <c r="AD37" t="n">
-        <v>9445683</v>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>9456605</t>
+        </is>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>Fortalecimento do Sistema Único de Saúde (SUS)</t>
+          <t>FORTALECIMENTO DA POLÍTICA PÚBLICA DE GESTÃO DO MANEJO DA FAUNA SILVESTRE, DE ACORDO COM MAPEAMENTO DE NECESSIDADES A SER DETALHADO, A PARTIR DE AÇÕES COMO DA ESTRUTURAÇÃO E CUSTEIO DOS SERVIÇOS PRESTADOS PELOS CETRAS QUE ATENDAM À BACIA HIDROGRÁFICA DO RIO DOCE; CONTRATAÇÃO DE SERVIÇOS VETERINÁRIOS ESPECIALIZADOS; CONSTRUÇÃO DE VIVEIROS EM ÁREAS DE PARCEIROS PARA A REABILITAÇÃO E CONSERVAÇÃO DA FAUNA</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 08 - 9445683 - Fortalecimento do Sistema Único de Saúde (SUS)</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9456605 - FORTALECIMENTO DA POLÍTICA PÚBLICA DE GESTÃO DO MANEJO DA FAUNA SILVESTRE, DE ACORDO COM MAPEAMENTO DE NECESSIDADES A SER DETALHADO, A PARTIR DE AÇÕES COMO DA ESTRUTURAÇÃO E CUSTEIO DOS SERVIÇOS PRESTADOS PELOS CETRAS QUE ATENDAM À BACIA HIDROGRÁFICA DO RIO DOCE; CONTRATAÇÃO DE SERVIÇOS VETERINÁRIOS ESPECIALIZADOS; CONSTRUÇÃO DE VIVEIROS EM ÁREAS DE PARCEIROS PARA A REABILITAÇÃO E CONSERVAÇÃO DA FAUNA</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B38" t="n">
         <v>1370</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>3</v>
       </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
       <c r="F38" t="n">
-        <v>1371</v>
+        <v>2101</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -4750,7 +4355,7 @@
         <v>90</v>
       </c>
       <c r="K38" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L38" t="n">
         <v>80</v>
@@ -4758,55 +4363,46 @@
       <c r="M38" t="n">
         <v>1</v>
       </c>
-      <c r="N38" t="n">
-        <v>9706</v>
-      </c>
       <c r="O38" t="n">
         <v>18</v>
       </c>
       <c r="P38" t="n">
-        <v>122</v>
+        <v>541</v>
       </c>
       <c r="Q38" t="n">
-        <v>705</v>
+        <v>31</v>
       </c>
       <c r="R38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S38" t="n">
-        <v>500</v>
+        <v>59</v>
       </c>
       <c r="T38" t="n">
-        <v>2500</v>
+        <v>4059</v>
       </c>
       <c r="U38" t="n">
         <v>1</v>
       </c>
-      <c r="V38" t="n">
-        <v>14656357</v>
-      </c>
-      <c r="W38" t="n">
-        <v>14656357</v>
-      </c>
       <c r="X38" t="n">
-        <v>14656357</v>
+        <v>3700000</v>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>ASSESSORAMENTO E GERENCIAMENTO DE POLÍTICAS PÚBLICAS</t>
+          <t>GESTÃO DE UNIDADES E CONSERVAÇÃO</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -4816,57 +4412,54 @@
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>INSTRUMENTO A SER CRIADO</t>
+          <t>9456606</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas ambientais</t>
+          <t>CONSOLIDAÇÃO DE UNIDADES DE CONSERVAÇÃO ESTADUAIS NA BACIA HIDROGRÁFICA DO RIO DOCE, A PARTIR DO INVESTIMENTO E CUSTEIO DE SUAS ESTRUTURAS E SERVIÇOS PRESTADOS, DE ACORDO COM SEUS OBJETIVOS DE CRIAÇÃO; CRIAÇÃO, SE NECESSÁRIO, DE NOVA(S) UNIDADE(S) DE CONSERVAÇÃO NA BACIA HIDROGRÁFICA DO RIO DOCE DE ACORDO COM MAPEAMENTO DE ÁREAS PRIORITÁRIAS PARA CONSERVAÇÃO; REALIZAÇÃO DE ATIVIDADES DE PREVENÇÃO E COMBATE A INCÊNDIOS E REGULARIZAÇÃO</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas ambientais</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9456606 - CONSOLIDAÇÃO DE UNIDADES DE CONSERVAÇÃO ESTADUAIS NA BACIA HIDROGRÁFICA DO RIO DOCE, A PARTIR DO INVESTIMENTO E CUSTEIO DE SUAS ESTRUTURAS E SERVIÇOS PRESTADOS, DE ACORDO COM SEUS OBJETIVOS DE CRIAÇÃO; CRIAÇÃO, SE NECESSÁRIO, DE NOVA(S) UNIDADE(S) DE CONSERVAÇÃO NA BACIA HIDROGRÁFICA DO RIO DOCE DE ACORDO COM MAPEAMENTO DE ÁREAS PRIORITÁRIAS PARA CONSERVAÇÃO; REALIZAÇÃO DE ATIVIDADES DE PREVENÇÃO E COMBATE A INCÊNDIOS E REGULARIZAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B39" t="n">
         <v>1370</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>3</v>
       </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
       <c r="F39" t="n">
-        <v>1371</v>
+        <v>2101</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J39" t="n">
         <v>90</v>
       </c>
       <c r="K39" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="L39" t="n">
         <v>80</v>
@@ -4874,95 +4467,83 @@
       <c r="M39" t="n">
         <v>1</v>
       </c>
-      <c r="N39" t="n">
-        <v>10255</v>
-      </c>
       <c r="O39" t="n">
         <v>18</v>
       </c>
       <c r="P39" t="n">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="Q39" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="R39" t="n">
         <v>4</v>
       </c>
       <c r="S39" t="n">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="T39" t="n">
-        <v>4038</v>
+        <v>4059</v>
       </c>
       <c r="U39" t="n">
         <v>1</v>
       </c>
-      <c r="V39" t="n">
-        <v>3160000</v>
-      </c>
-      <c r="W39" t="n">
-        <v>3160000</v>
-      </c>
       <c r="X39" t="n">
-        <v>3160000</v>
+        <v>1000000</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>FISCALIZAÇÃO AMBIENTAL</t>
+          <t>GESTÃO DE UNIDADES E CONSERVAÇÃO</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>MONITORAMENTO, CONTROLE E FISCALIZAÇÃO AMBIENTAL</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>ANEXO 12</t>
+          <t>ANEXO 10</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>INSTRUMENTO A SER CRIADO</t>
+          <t>9445703</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>Melhoria na capacidade estadual fiscalizatória de barragens nas estruturas localizadas na extensão territorial da Bacia Hidrográfica do Rio Doce: aquisição de equipamentos físicos e tecnológicos, contratação de serviços de consultoria</t>
+          <t>IMPLEMENTAÇÃO E POSTERIOR MANUTENÇÃO, PELO ESTDO DE MINAS GERAIS, DE UNIDADE DE CONSERVAÇÃO DE PROTEÇÃO INTEGRAL NO BIOMA MATA ATLANTICA, A FIM DE CONTRIBUIR PARA A PRESERVAÇÃO DO RIO SANTO ANTONIO E PARA A RECUPERAÇÃO DOS ESTOQUES PESQUEIROS DO RIO DOCE</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Melhoria na capacidade estadual fiscalizatória de barragens nas estruturas localizadas na extensão territorial da Bacia Hidrográfica do Rio Doce: aquisição de equipamentos físicos e tecnológicos, contratação de serviços de consultoria</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 10 - 9445703 - IMPLEMENTAÇÃO E POSTERIOR MANUTENÇÃO, PELO ESTDO DE MINAS GERAIS, DE UNIDADE DE CONSERVAÇÃO DE PROTEÇÃO INTEGRAL NO BIOMA MATA ATLANTICA, A FIM DE CONTRIBUIR PARA A PRESERVAÇÃO DO RIO SANTO ANTONIO E PARA A RECUPERAÇÃO DOS ESTOQUES PESQUEIROS DO RIO DOCE</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B40" t="n">
         <v>1370</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D40" t="n">
         <v>3</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0</v>
       </c>
       <c r="F40" t="n">
         <v>2101</v>
@@ -4982,7 +4563,7 @@
         <v>90</v>
       </c>
       <c r="K40" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L40" t="n">
         <v>80</v>
@@ -4990,9 +4571,6 @@
       <c r="M40" t="n">
         <v>1</v>
       </c>
-      <c r="N40" t="n">
-        <v>10271</v>
-      </c>
       <c r="O40" t="n">
         <v>18</v>
       </c>
@@ -5006,29 +4584,23 @@
         <v>4</v>
       </c>
       <c r="S40" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="T40" t="n">
-        <v>4054</v>
+        <v>4059</v>
       </c>
       <c r="U40" t="n">
         <v>1</v>
       </c>
-      <c r="V40" t="n">
-        <v>7853980</v>
-      </c>
-      <c r="W40" t="n">
-        <v>7853980</v>
-      </c>
       <c r="X40" t="n">
-        <v>7853980</v>
+        <v>100000</v>
       </c>
       <c r="Y40" t="n">
         <v>0</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>PREVENÇÃO E COMBATE A INCÊNDIOS FLORESTAIS</t>
+          <t>GESTÃO DE UNIDADES E CONSERVAÇÃO</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5038,7 +4610,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5046,37 +4618,36 @@
           <t>ANEXO 12</t>
         </is>
       </c>
-      <c r="AD40" t="n">
-        <v>9456606</v>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>9468057</t>
+        </is>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>Consolidação de unidades de conservação estaduais na Bacia Hidrográfica do Rio Doce, a partir do investimento e custeio de suas estruturas e serviços prestados, de acordo com seus objetivos de criação; criação, se necessário, de nova(s) unidade(s) de conservação na Bacia Hidrográfica do Rio Doce de acordo com mapeamento de áreas prioritárias para conservação; realização de atividades de prevenção e combate a incêndios e regularização fundiária das unidades de conservação</t>
+          <t>SUPORTE GERENCIAL, ADMINISTRATIVO, TECNOLÓGICO E DE COMUNICAÇÃO SOCIAL</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456606 - Consolidação de unidades de conservação estaduais na Bacia Hidrográfica do Rio Doce, a partir do investimento e custeio de suas estruturas e serviços prestados, de acordo com seus objetivos de criação; criação, se necessário, de nova(s) unidade(s) de conservação na Bacia Hidrográfica do Rio Doce de acordo com mapeamento de áreas prioritárias para conservação; realização de atividades de prevenção e combate a incêndios e regularização fundiária das unidades de conservação</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9468057 - SUPORTE GERENCIAL, ADMINISTRATIVO, TECNOLÓGICO E DE COMUNICAÇÃO SOCIAL</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B41" t="n">
         <v>1370</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D41" t="n">
         <v>3</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>2101</v>
@@ -5087,16 +4658,16 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J41" t="n">
         <v>90</v>
       </c>
       <c r="K41" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="L41" t="n">
         <v>80</v>
@@ -5104,9 +4675,6 @@
       <c r="M41" t="n">
         <v>1</v>
       </c>
-      <c r="N41" t="n">
-        <v>10271</v>
-      </c>
       <c r="O41" t="n">
         <v>18</v>
       </c>
@@ -5120,29 +4688,23 @@
         <v>4</v>
       </c>
       <c r="S41" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="T41" t="n">
-        <v>4054</v>
+        <v>4059</v>
       </c>
       <c r="U41" t="n">
         <v>1</v>
       </c>
-      <c r="V41" t="n">
-        <v>1566500</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1566500</v>
-      </c>
       <c r="X41" t="n">
-        <v>1566500</v>
+        <v>1000000</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>PREVENÇÃO E COMBATE A INCÊNDIOS FLORESTAIS</t>
+          <t>GESTÃO DE UNIDADES E CONSERVAÇÃO</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5152,45 +4714,44 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>ANEXO 12</t>
-        </is>
-      </c>
-      <c r="AD41" t="n">
-        <v>9456606</v>
+          <t>ANEXO 10</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>9445703</t>
+        </is>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>Consolidação de unidades de conservação estaduais na Bacia Hidrográfica do Rio Doce, a partir do investimento e custeio de suas estruturas e serviços prestados, de acordo com seus objetivos de criação; criação, se necessário, de nova(s) unidade(s) de conservação na Bacia Hidrográfica do Rio Doce de acordo com mapeamento de áreas prioritárias para conservação; realização de atividades de prevenção e combate a incêndios e regularização fundiária das unidades de conservação</t>
+          <t>IMPLEMENTAÇÃO E POSTERIOR MANUTENÇÃO, PELO ESTDO DE MINAS GERAIS, DE UNIDADE DE CONSERVAÇÃO DE PROTEÇÃO INTEGRAL NO BIOMA MATA ATLANTICA, A FIM DE CONTRIBUIR PARA A PRESERVAÇÃO DO RIO SANTO ANTONIO E PARA A RECUPERAÇÃO DOS ESTOQUES PESQUEIROS DO RIO DOCE</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456606 - Consolidação de unidades de conservação estaduais na Bacia Hidrográfica do Rio Doce, a partir do investimento e custeio de suas estruturas e serviços prestados, de acordo com seus objetivos de criação; criação, se necessário, de nova(s) unidade(s) de conservação na Bacia Hidrográfica do Rio Doce de acordo com mapeamento de áreas prioritárias para conservação; realização de atividades de prevenção e combate a incêndios e regularização fundiária das unidades de conservação</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 10 - 9445703 - IMPLEMENTAÇÃO E POSTERIOR MANUTENÇÃO, PELO ESTDO DE MINAS GERAIS, DE UNIDADE DE CONSERVAÇÃO DE PROTEÇÃO INTEGRAL NO BIOMA MATA ATLANTICA, A FIM DE CONTRIBUIR PARA A PRESERVAÇÃO DO RIO SANTO ANTONIO E PARA A RECUPERAÇÃO DOS ESTOQUES PESQUEIROS DO RIO DOCE</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B42" t="n">
         <v>1370</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>3</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>2101</v>
@@ -5207,10 +4768,10 @@
         <v>3</v>
       </c>
       <c r="J42" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="K42" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="L42" t="n">
         <v>80</v>
@@ -5218,9 +4779,6 @@
       <c r="M42" t="n">
         <v>1</v>
       </c>
-      <c r="N42" t="n">
-        <v>10275</v>
-      </c>
       <c r="O42" t="n">
         <v>18</v>
       </c>
@@ -5234,29 +4792,23 @@
         <v>4</v>
       </c>
       <c r="S42" t="n">
-        <v>58</v>
+        <v>500</v>
       </c>
       <c r="T42" t="n">
-        <v>4058</v>
+        <v>4500</v>
       </c>
       <c r="U42" t="n">
         <v>1</v>
       </c>
-      <c r="V42" t="n">
-        <v>10024938</v>
-      </c>
-      <c r="W42" t="n">
-        <v>10024938</v>
-      </c>
       <c r="X42" t="n">
-        <v>10024938</v>
+        <v>1500000</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>PROTEÇÃO E CONSERVAÇÃO DA FAUNA SILVESTRE</t>
+          <t>REGULARIZAÇÃO FUNDIÁRIA DE UNIDADES DE CONSERVAÇÃO</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5266,47 +4818,44 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>ANEXO 10</t>
+          <t>ANEXO 12</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>INSTRUMENTO A SER CRIADO</t>
+          <t>9456606</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Elaboração e/ou atualização do ordenamento pesqueiro, na forma da Lei n. 11.959, de 29 de junho de 2009. III. Recomposição da biota, dos recursos e dos estoques pesqueiros do ecossistema como um todo na Bacia Hidrográfica do rio Doce, em sua foz e região costeira e marinha.</t>
+          <t>CONSOLIDAÇÃO DE UNIDADES DE CONSERVAÇÃO ESTADUAIS NA BACIA HIDROGRÁFICA DO RIO DOCE, A PARTIR DO INVESTIMENTO E CUSTEIO DE SUAS ESTRUTURAS E SERVIÇOS PRESTADOS, DE ACORDO COM SEUS OBJETIVOS DE CRIAÇÃO; CRIAÇÃO, SE NECESSÁRIO, DE NOVA(S) UNIDADE(S) DE CONSERVAÇÃO NA BACIA HIDROGRÁFICA DO RIO DOCE DE ACORDO COM MAPEAMENTO DE ÁREAS PRIORITÁRIAS PARA CONSERVAÇÃO; REALIZAÇÃO DE ATIVIDADES DE PREVENÇÃO E COMBATE A INCÊNDIOS E REGULARIZAÇÃO</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 10 - INSTRUMENTO A SER CRIADO -  Elaboração e/ou atualização do ordenamento pesqueiro, na forma da Lei n. 11.959, de 29 de junho de 2009. III. Recomposição da biota, dos recursos e dos estoques pesqueiros do ecossistema como um todo na Bacia Hidrográfica do rio Doce, em sua foz e região costeira e marinha.</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9456606 - CONSOLIDAÇÃO DE UNIDADES DE CONSERVAÇÃO ESTADUAIS NA BACIA HIDROGRÁFICA DO RIO DOCE, A PARTIR DO INVESTIMENTO E CUSTEIO DE SUAS ESTRUTURAS E SERVIÇOS PRESTADOS, DE ACORDO COM SEUS OBJETIVOS DE CRIAÇÃO; CRIAÇÃO, SE NECESSÁRIO, DE NOVA(S) UNIDADE(S) DE CONSERVAÇÃO NA BACIA HIDROGRÁFICA DO RIO DOCE DE ACORDO COM MAPEAMENTO DE ÁREAS PRIORITÁRIAS PARA CONSERVAÇÃO; REALIZAÇÃO DE ATIVIDADES DE PREVENÇÃO E COMBATE A INCÊNDIOS E REGULARIZAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B43" t="n">
         <v>1370</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D43" t="n">
         <v>3</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0</v>
       </c>
       <c r="F43" t="n">
         <v>2101</v>
@@ -5317,16 +4866,16 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J43" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="K43" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L43" t="n">
         <v>80</v>
@@ -5334,9 +4883,6 @@
       <c r="M43" t="n">
         <v>1</v>
       </c>
-      <c r="N43" t="n">
-        <v>10275</v>
-      </c>
       <c r="O43" t="n">
         <v>18</v>
       </c>
@@ -5350,29 +4896,23 @@
         <v>4</v>
       </c>
       <c r="S43" t="n">
-        <v>58</v>
+        <v>500</v>
       </c>
       <c r="T43" t="n">
-        <v>4058</v>
+        <v>4500</v>
       </c>
       <c r="U43" t="n">
         <v>1</v>
       </c>
-      <c r="V43" t="n">
-        <v>3392647</v>
-      </c>
-      <c r="W43" t="n">
-        <v>3392647</v>
-      </c>
       <c r="X43" t="n">
-        <v>3392647</v>
+        <v>100000</v>
       </c>
       <c r="Y43" t="n">
         <v>0</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>PROTEÇÃO E CONSERVAÇÃO DA FAUNA SILVESTRE</t>
+          <t>REGULARIZAÇÃO FUNDIÁRIA DE UNIDADES DE CONSERVAÇÃO</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5382,7 +4922,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -5390,37 +4930,36 @@
           <t>ANEXO 12</t>
         </is>
       </c>
-      <c r="AD43" t="n">
-        <v>9456605</v>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>9456606</t>
+        </is>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>Fortalecimento da política pública de gestão do manejo da fauna silvestre, de acordo com mapeamento de necessidades a ser detalhado, a partir de ações como da estruturação e custeio dos serviços prestados pelos Cetras que atendam à bacia hidrográfica do rio Doce; contratação de serviços veterinários especializados; construção de viveiros em áreas de parceiros para a reabilitação e conservação da fauna</t>
+          <t>CONSOLIDAÇÃO DE UNIDADES DE CONSERVAÇÃO ESTADUAIS NA BACIA HIDROGRÁFICA DO RIO DOCE, A PARTIR DO INVESTIMENTO E CUSTEIO DE SUAS ESTRUTURAS E SERVIÇOS PRESTADOS, DE ACORDO COM SEUS OBJETIVOS DE CRIAÇÃO; CRIAÇÃO, SE NECESSÁRIO, DE NOVA(S) UNIDADE(S) DE CONSERVAÇÃO NA BACIA HIDROGRÁFICA DO RIO DOCE DE ACORDO COM MAPEAMENTO DE ÁREAS PRIORITÁRIAS PARA CONSERVAÇÃO; REALIZAÇÃO DE ATIVIDADES DE PREVENÇÃO E COMBATE A INCÊNDIOS E REGULARIZAÇÃO</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456605 - Fortalecimento da política pública de gestão do manejo da fauna silvestre, de acordo com mapeamento de necessidades a ser detalhado, a partir de ações como da estruturação e custeio dos serviços prestados pelos Cetras que atendam à bacia hidrográfica do rio Doce; contratação de serviços veterinários especializados; construção de viveiros em áreas de parceiros para a reabilitação e conservação da fauna</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9456606 - CONSOLIDAÇÃO DE UNIDADES DE CONSERVAÇÃO ESTADUAIS NA BACIA HIDROGRÁFICA DO RIO DOCE, A PARTIR DO INVESTIMENTO E CUSTEIO DE SUAS ESTRUTURAS E SERVIÇOS PRESTADOS, DE ACORDO COM SEUS OBJETIVOS DE CRIAÇÃO; CRIAÇÃO, SE NECESSÁRIO, DE NOVA(S) UNIDADE(S) DE CONSERVAÇÃO NA BACIA HIDROGRÁFICA DO RIO DOCE DE ACORDO COM MAPEAMENTO DE ÁREAS PRIORITÁRIAS PARA CONSERVAÇÃO; REALIZAÇÃO DE ATIVIDADES DE PREVENÇÃO E COMBATE A INCÊNDIOS E REGULARIZAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B44" t="n">
         <v>1370</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D44" t="n">
         <v>3</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>2101</v>
@@ -5431,16 +4970,16 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J44" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="K44" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="L44" t="n">
         <v>80</v>
@@ -5448,9 +4987,6 @@
       <c r="M44" t="n">
         <v>1</v>
       </c>
-      <c r="N44" t="n">
-        <v>10275</v>
-      </c>
       <c r="O44" t="n">
         <v>18</v>
       </c>
@@ -5464,29 +5000,23 @@
         <v>4</v>
       </c>
       <c r="S44" t="n">
-        <v>58</v>
+        <v>500</v>
       </c>
       <c r="T44" t="n">
-        <v>4058</v>
+        <v>4500</v>
       </c>
       <c r="U44" t="n">
         <v>1</v>
       </c>
-      <c r="V44" t="n">
-        <v>10542587</v>
-      </c>
-      <c r="W44" t="n">
-        <v>10542587</v>
-      </c>
       <c r="X44" t="n">
-        <v>10542587</v>
+        <v>200000</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>PROTEÇÃO E CONSERVAÇÃO DA FAUNA SILVESTRE</t>
+          <t>REGULARIZAÇÃO FUNDIÁRIA DE UNIDADES DE CONSERVAÇÃO</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5496,7 +5026,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -5504,37 +5034,36 @@
           <t>ANEXO 12</t>
         </is>
       </c>
-      <c r="AD44" t="n">
-        <v>9456612</v>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>9456606</t>
+        </is>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>Revitalização aquática da Bacia Hidrográfica do rio Doce, a partir do mapeamento de áreas estratégicas para revitalização e conservação da fauna e flora aquáticas, em especial áreas de cabeceiras, tributários e rotas de piracema, e execução de ações como zoneamento pesqueiro; desassoreamento; reconformação de calhas de rios; renaturalização de leitos de rios; reintrodução de espécies aquáticas ameaçadas; educação ambiental, dentre outras ações baseadas na natureza para a revitalização intracalha do rio Doce e seus tributários</t>
+          <t>CONSOLIDAÇÃO DE UNIDADES DE CONSERVAÇÃO ESTADUAIS NA BACIA HIDROGRÁFICA DO RIO DOCE, A PARTIR DO INVESTIMENTO E CUSTEIO DE SUAS ESTRUTURAS E SERVIÇOS PRESTADOS, DE ACORDO COM SEUS OBJETIVOS DE CRIAÇÃO; CRIAÇÃO, SE NECESSÁRIO, DE NOVA(S) UNIDADE(S) DE CONSERVAÇÃO NA BACIA HIDROGRÁFICA DO RIO DOCE DE ACORDO COM MAPEAMENTO DE ÁREAS PRIORITÁRIAS PARA CONSERVAÇÃO; REALIZAÇÃO DE ATIVIDADES DE PREVENÇÃO E COMBATE A INCÊNDIOS E REGULARIZAÇÃO</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456612 - Revitalização aquática da Bacia Hidrográfica do rio Doce, a partir do mapeamento de áreas estratégicas para revitalização e conservação da fauna e flora aquáticas, em especial áreas de cabeceiras, tributários e rotas de piracema, e execução de ações como zoneamento pesqueiro; desassoreamento; reconformação de calhas de rios; renaturalização de leitos de rios; reintrodução de espécies aquáticas ameaçadas; educação ambiental, dentre outras ações baseadas na natureza para a revitalização intracalha do rio Doce e seus tributários</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9456606 - CONSOLIDAÇÃO DE UNIDADES DE CONSERVAÇÃO ESTADUAIS NA BACIA HIDROGRÁFICA DO RIO DOCE, A PARTIR DO INVESTIMENTO E CUSTEIO DE SUAS ESTRUTURAS E SERVIÇOS PRESTADOS, DE ACORDO COM SEUS OBJETIVOS DE CRIAÇÃO; CRIAÇÃO, SE NECESSÁRIO, DE NOVA(S) UNIDADE(S) DE CONSERVAÇÃO NA BACIA HIDROGRÁFICA DO RIO DOCE DE ACORDO COM MAPEAMENTO DE ÁREAS PRIORITÁRIAS PARA CONSERVAÇÃO; REALIZAÇÃO DE ATIVIDADES DE PREVENÇÃO E COMBATE A INCÊNDIOS E REGULARIZAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B45" t="n">
         <v>1370</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D45" t="n">
         <v>3</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>2101</v>
@@ -5545,16 +5074,16 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J45" t="n">
         <v>90</v>
       </c>
       <c r="K45" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="L45" t="n">
         <v>80</v>
@@ -5562,9 +5091,6 @@
       <c r="M45" t="n">
         <v>1</v>
       </c>
-      <c r="N45" t="n">
-        <v>10275</v>
-      </c>
       <c r="O45" t="n">
         <v>18</v>
       </c>
@@ -5578,29 +5104,23 @@
         <v>4</v>
       </c>
       <c r="S45" t="n">
-        <v>58</v>
+        <v>500</v>
       </c>
       <c r="T45" t="n">
-        <v>4058</v>
+        <v>4500</v>
       </c>
       <c r="U45" t="n">
         <v>1</v>
       </c>
-      <c r="V45" t="n">
-        <v>726819</v>
-      </c>
-      <c r="W45" t="n">
-        <v>726819</v>
-      </c>
       <c r="X45" t="n">
-        <v>726819</v>
+        <v>13000000</v>
       </c>
       <c r="Y45" t="n">
         <v>0</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>PROTEÇÃO E CONSERVAÇÃO DA FAUNA SILVESTRE</t>
+          <t>REGULARIZAÇÃO FUNDIÁRIA DE UNIDADES DE CONSERVAÇÃO</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5610,7 +5130,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -5618,37 +5138,36 @@
           <t>ANEXO 12</t>
         </is>
       </c>
-      <c r="AD45" t="n">
-        <v>9456605</v>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>9456606</t>
+        </is>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>Fortalecimento da política pública de gestão do manejo da fauna silvestre, de acordo com mapeamento de necessidades a ser detalhado, a partir de ações como da estruturação e custeio dos serviços prestados porelos Cetras que atendam à bacia hidrográfica do rio Doce; contratação de serviços veterinários especializados; construção de viveiros em áreas de parceiros para a reabilitação e conservação da faunA</t>
+          <t>CONSOLIDAÇÃO DE UNIDADES DE CONSERVAÇÃO ESTADUAIS NA BACIA HIDROGRÁFICA DO RIO DOCE, A PARTIR DO INVESTIMENTO E CUSTEIO DE SUAS ESTRUTURAS E SERVIÇOS PRESTADOS, DE ACORDO COM SEUS OBJETIVOS DE CRIAÇÃO; CRIAÇÃO, SE NECESSÁRIO, DE NOVA(S) UNIDADE(S) DE CONSERVAÇÃO NA BACIA HIDROGRÁFICA DO RIO DOCE DE ACORDO COM MAPEAMENTO DE ÁREAS PRIORITÁRIAS PARA CONSERVAÇÃO; REALIZAÇÃO DE ATIVIDADES DE PREVENÇÃO E COMBATE A INCÊNDIOS E REGULARIZAÇÃO</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456605 - Fortalecimento da política pública de gestão do manejo da fauna silvestre, de acordo com mapeamento de necessidades a ser detalhado, a partir de ações como da estruturação e custeio dos serviços prestados porelos Cetras que atendam à bacia hidrográfica do rio Doce; contratação de serviços veterinários especializados; construção de viveiros em áreas de parceiros para a reabilitação e conservação da faunA</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9456606 - CONSOLIDAÇÃO DE UNIDADES DE CONSERVAÇÃO ESTADUAIS NA BACIA HIDROGRÁFICA DO RIO DOCE, A PARTIR DO INVESTIMENTO E CUSTEIO DE SUAS ESTRUTURAS E SERVIÇOS PRESTADOS, DE ACORDO COM SEUS OBJETIVOS DE CRIAÇÃO; CRIAÇÃO, SE NECESSÁRIO, DE NOVA(S) UNIDADE(S) DE CONSERVAÇÃO NA BACIA HIDROGRÁFICA DO RIO DOCE DE ACORDO COM MAPEAMENTO DE ÁREAS PRIORITÁRIAS PARA CONSERVAÇÃO; REALIZAÇÃO DE ATIVIDADES DE PREVENÇÃO E COMBATE A INCÊNDIOS E REGULARIZAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B46" t="n">
         <v>1370</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D46" t="n">
         <v>3</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>2101</v>
@@ -5665,10 +5184,10 @@
         <v>3</v>
       </c>
       <c r="J46" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="K46" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L46" t="n">
         <v>80</v>
@@ -5676,14 +5195,11 @@
       <c r="M46" t="n">
         <v>1</v>
       </c>
-      <c r="N46" t="n">
-        <v>10275</v>
-      </c>
       <c r="O46" t="n">
         <v>18</v>
       </c>
       <c r="P46" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="Q46" t="n">
         <v>31</v>
@@ -5692,29 +5208,23 @@
         <v>4</v>
       </c>
       <c r="S46" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="T46" t="n">
-        <v>4058</v>
+        <v>4056</v>
       </c>
       <c r="U46" t="n">
         <v>1</v>
       </c>
-      <c r="V46" t="n">
-        <v>85000</v>
-      </c>
-      <c r="W46" t="n">
-        <v>85000</v>
-      </c>
       <c r="X46" t="n">
-        <v>85000</v>
+        <v>440000</v>
       </c>
       <c r="Y46" t="n">
         <v>0</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>PROTEÇÃO E CONSERVAÇÃO DA FAUNA SILVESTRE</t>
+          <t>RECUPERAÇÃO AMBIENTAL</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5724,7 +5234,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5732,37 +5242,36 @@
           <t>ANEXO 12</t>
         </is>
       </c>
-      <c r="AD46" t="n">
-        <v>9456612</v>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>9445719</t>
+        </is>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>Revitalização aquática da Bacia Hidrográfica do rio Doce, a partir do mapeamento de áreas estratégicas para revitalização e conservação da fauna e flora aquáticas, em especial áreas de cabeceiras, tributários e rotas de piracema, e execução de ações como zoneamento pesqueiro; desassoreamento; reconformação de calhas de rios; renaturalização de leitos de rios; reintrodução de espécies aquáticas ameaçadas; educação ambiental, dentre outras ações baseadas na natureza para a revitalização intracalha do rio Doce e seus tributários</t>
+          <t>RECUPERAÇÃO DA VEGETAÇÃO NATIVA NA BACIA HIDROGRÁFICA DO RIO DOCE, COM PRIORIDADE ÀS ÁREAS DE MATA RIPÁRIA, POR MEIO DE AÇÕES DE REFLORESTAMENTO, PAGAMENTO DE SERVIÇOS AMBIENTAIS, MAPEAMENTO DO USO DE SOLO E INVESTIMENTO TECNOLÓGICO PARA MONITORAMENTO DA VEGETAÇÃO NATIVA E SUA RECUPERAÇÃO</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456612 - Revitalização aquática da Bacia Hidrográfica do rio Doce, a partir do mapeamento de áreas estratégicas para revitalização e conservação da fauna e flora aquáticas, em especial áreas de cabeceiras, tributários e rotas de piracema, e execução de ações como zoneamento pesqueiro; desassoreamento; reconformação de calhas de rios; renaturalização de leitos de rios; reintrodução de espécies aquáticas ameaçadas; educação ambiental, dentre outras ações baseadas na natureza para a revitalização intracalha do rio Doce e seus tributários</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9445719 - RECUPERAÇÃO DA VEGETAÇÃO NATIVA NA BACIA HIDROGRÁFICA DO RIO DOCE, COM PRIORIDADE ÀS ÁREAS DE MATA RIPÁRIA, POR MEIO DE AÇÕES DE REFLORESTAMENTO, PAGAMENTO DE SERVIÇOS AMBIENTAIS, MAPEAMENTO DO USO DE SOLO E INVESTIMENTO TECNOLÓGICO PARA MONITORAMENTO DA VEGETAÇÃO NATIVA E SUA RECUPERAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B47" t="n">
         <v>1370</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D47" t="n">
         <v>3</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0</v>
       </c>
       <c r="F47" t="n">
         <v>2101</v>
@@ -5782,7 +5291,7 @@
         <v>50</v>
       </c>
       <c r="K47" t="n">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="L47" t="n">
         <v>80</v>
@@ -5790,14 +5299,11 @@
       <c r="M47" t="n">
         <v>1</v>
       </c>
-      <c r="N47" t="n">
-        <v>10276</v>
-      </c>
       <c r="O47" t="n">
         <v>18</v>
       </c>
       <c r="P47" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="Q47" t="n">
         <v>31</v>
@@ -5806,29 +5312,23 @@
         <v>4</v>
       </c>
       <c r="S47" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="T47" t="n">
-        <v>4059</v>
+        <v>4056</v>
       </c>
       <c r="U47" t="n">
         <v>1</v>
       </c>
-      <c r="V47" t="n">
-        <v>14093425</v>
-      </c>
-      <c r="W47" t="n">
-        <v>14093425</v>
-      </c>
       <c r="X47" t="n">
-        <v>14093425</v>
+        <v>19200000</v>
       </c>
       <c r="Y47" t="n">
         <v>0</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>GESTÃO DE UNIDADES E CONSERVAÇÃO</t>
+          <t>RECUPERAÇÃO AMBIENTAL</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5838,7 +5338,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -5846,37 +5346,36 @@
           <t>ANEXO 12</t>
         </is>
       </c>
-      <c r="AD47" t="n">
-        <v>9456606</v>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>9445719</t>
+        </is>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>Consolidação de unidades de conservação estaduais na Bacia Hidrográfica do Rio Doce, a partir do investimento e custeio de suas estruturas e serviços prestados, de acordo com seus objetivos de criação; criação, se necessário, de nova(s) unidade(s) de conservação na Bacia Hidrográfica do Rio Doce de acordo com mapeamento de áreas prioritárias para conservação; realização de atividades de prevenção e combate a incêndios e regularização fundiária das unidades de conservação</t>
+          <t>RECUPERAÇÃO DA VEGETAÇÃO NATIVA NA BACIA HIDROGRÁFICA DO RIO DOCE, COM PRIORIDADE ÀS ÁREAS DE MATA RIPÁRIA, POR MEIO DE AÇÕES DE REFLORESTAMENTO, PAGAMENTO DE SERVIÇOS AMBIENTAIS, MAPEAMENTO DO USO DE SOLO E INVESTIMENTO TECNOLÓGICO PARA MONITORAMENTO DA VEGETAÇÃO NATIVA E SUA RECUPERAÇÃO</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456606 - Consolidação de unidades de conservação estaduais na Bacia Hidrográfica do Rio Doce, a partir do investimento e custeio de suas estruturas e serviços prestados, de acordo com seus objetivos de criação; criação, se necessário, de nova(s) unidade(s) de conservação na Bacia Hidrográfica do Rio Doce de acordo com mapeamento de áreas prioritárias para conservação; realização de atividades de prevenção e combate a incêndios e regularização fundiária das unidades de conservação</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9445719 - RECUPERAÇÃO DA VEGETAÇÃO NATIVA NA BACIA HIDROGRÁFICA DO RIO DOCE, COM PRIORIDADE ÀS ÁREAS DE MATA RIPÁRIA, POR MEIO DE AÇÕES DE REFLORESTAMENTO, PAGAMENTO DE SERVIÇOS AMBIENTAIS, MAPEAMENTO DO USO DE SOLO E INVESTIMENTO TECNOLÓGICO PARA MONITORAMENTO DA VEGETAÇÃO NATIVA E SUA RECUPERAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B48" t="n">
         <v>1370</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D48" t="n">
         <v>3</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0</v>
       </c>
       <c r="F48" t="n">
         <v>2101</v>
@@ -5896,7 +5395,7 @@
         <v>90</v>
       </c>
       <c r="K48" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L48" t="n">
         <v>80</v>
@@ -5904,14 +5403,11 @@
       <c r="M48" t="n">
         <v>1</v>
       </c>
-      <c r="N48" t="n">
-        <v>11201</v>
-      </c>
       <c r="O48" t="n">
         <v>18</v>
       </c>
       <c r="P48" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="Q48" t="n">
         <v>31</v>
@@ -5920,29 +5416,23 @@
         <v>4</v>
       </c>
       <c r="S48" t="n">
-        <v>500</v>
+        <v>56</v>
       </c>
       <c r="T48" t="n">
-        <v>4500</v>
+        <v>4056</v>
       </c>
       <c r="U48" t="n">
         <v>1</v>
       </c>
-      <c r="V48" t="n">
-        <v>13318032</v>
-      </c>
-      <c r="W48" t="n">
-        <v>13318032</v>
-      </c>
       <c r="X48" t="n">
-        <v>13318032</v>
+        <v>360000</v>
       </c>
       <c r="Y48" t="n">
         <v>0</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>REGULARIZAÇÃO FUNDIÁRIA DE UNIDADES DE CONSERVAÇÃO</t>
+          <t>RECUPERAÇÃO AMBIENTAL</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5952,7 +5442,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -5960,37 +5450,36 @@
           <t>ANEXO 12</t>
         </is>
       </c>
-      <c r="AD48" t="n">
-        <v>9456606</v>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>9445719</t>
+        </is>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>Consolidação de unidades de conservação estaduais na Bacia Hidrográfica do Rio Doce, a partir do investimento e custeio de suas estruturas e serviços prestados, de acordo com seus objetivos de criação; criação, se necessário, de nova(s) unidade(s) de conservação na Bacia Hidrográfica do Rio Doce de acordo com mapeamento de áreas prioritárias para conservação; realização de atividades de prevenção e combate a incêndios e regularização fundiária das unidades de conservação</t>
+          <t>RECUPERAÇÃO DA VEGETAÇÃO NATIVA NA BACIA HIDROGRÁFICA DO RIO DOCE, COM PRIORIDADE ÀS ÁREAS DE MATA RIPÁRIA, POR MEIO DE AÇÕES DE REFLORESTAMENTO, PAGAMENTO DE SERVIÇOS AMBIENTAIS, MAPEAMENTO DO USO DE SOLO E INVESTIMENTO TECNOLÓGICO PARA MONITORAMENTO DA VEGETAÇÃO NATIVA E SUA RECUPERAÇÃO</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456606 - Consolidação de unidades de conservação estaduais na Bacia Hidrográfica do Rio Doce, a partir do investimento e custeio de suas estruturas e serviços prestados, de acordo com seus objetivos de criação; criação, se necessário, de nova(s) unidade(s) de conservação na Bacia Hidrográfica do Rio Doce de acordo com mapeamento de áreas prioritárias para conservação; realização de atividades de prevenção e combate a incêndios e regularização fundiária das unidades de conservação</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9445719 - RECUPERAÇÃO DA VEGETAÇÃO NATIVA NA BACIA HIDROGRÁFICA DO RIO DOCE, COM PRIORIDADE ÀS ÁREAS DE MATA RIPÁRIA, POR MEIO DE AÇÕES DE REFLORESTAMENTO, PAGAMENTO DE SERVIÇOS AMBIENTAIS, MAPEAMENTO DO USO DE SOLO E INVESTIMENTO TECNOLÓGICO PARA MONITORAMENTO DA VEGETAÇÃO NATIVA E SUA RECUPERAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B49" t="n">
         <v>1370</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D49" t="n">
         <v>3</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>2101</v>
@@ -6001,16 +5490,16 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J49" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="K49" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L49" t="n">
         <v>80</v>
@@ -6018,9 +5507,6 @@
       <c r="M49" t="n">
         <v>1</v>
       </c>
-      <c r="N49" t="n">
-        <v>10273</v>
-      </c>
       <c r="O49" t="n">
         <v>18</v>
       </c>
@@ -6042,14 +5528,8 @@
       <c r="U49" t="n">
         <v>1</v>
       </c>
-      <c r="V49" t="n">
-        <v>22582986</v>
-      </c>
-      <c r="W49" t="n">
-        <v>22582986</v>
-      </c>
       <c r="X49" t="n">
-        <v>22582986</v>
+        <v>1000000</v>
       </c>
       <c r="Y49" t="n">
         <v>0</v>
@@ -6066,7 +5546,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -6074,57 +5554,56 @@
           <t>ANEXO 12</t>
         </is>
       </c>
-      <c r="AD49" t="n">
-        <v>9445719</v>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>9445719</t>
+        </is>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>Recuperação da vegetação nativa na Bacia Hidrográfica do Rio Doce, com prioridade às áreas de mata ripária, por meio de ações de reflorestamento, pagamento de serviços ambientais, mapeamento do uso de solo e investimento tecnológico para monitoramento da vegetação nativa e sua recuperação</t>
+          <t>RECUPERAÇÃO DA VEGETAÇÃO NATIVA NA BACIA HIDROGRÁFICA DO RIO DOCE, COM PRIORIDADE ÀS ÁREAS DE MATA RIPÁRIA, POR MEIO DE AÇÕES DE REFLORESTAMENTO, PAGAMENTO DE SERVIÇOS AMBIENTAIS, MAPEAMENTO DO USO DE SOLO E INVESTIMENTO TECNOLÓGICO PARA MONITORAMENTO DA VEGETAÇÃO NATIVA E SUA RECUPERAÇÃO</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9445719 - Recuperação da vegetação nativa na Bacia Hidrográfica do Rio Doce, com prioridade às áreas de mata ripária, por meio de ações de reflorestamento, pagamento de serviços ambientais, mapeamento do uso de solo e investimento tecnológico para monitoramento da vegetação nativa e sua recuperação</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9445719 - RECUPERAÇÃO DA VEGETAÇÃO NATIVA NA BACIA HIDROGRÁFICA DO RIO DOCE, COM PRIORIDADE ÀS ÁREAS DE MATA RIPÁRIA, POR MEIO DE AÇÕES DE REFLORESTAMENTO, PAGAMENTO DE SERVIÇOS AMBIENTAIS, MAPEAMENTO DO USO DE SOLO E INVESTIMENTO TECNOLÓGICO PARA MONITORAMENTO DA VEGETAÇÃO NATIVA E SUA RECUPERAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B50" t="n">
         <v>1370</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IEF</t>
         </is>
       </c>
       <c r="D50" t="n">
         <v>3</v>
       </c>
-      <c r="E50" t="n">
-        <v>0</v>
-      </c>
       <c r="F50" t="n">
-        <v>2241</v>
+        <v>2101</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE GESTÃO DAS ÁGUAS - IGAM</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS - IEF</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J50" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="K50" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="L50" t="n">
         <v>80</v>
@@ -6132,55 +5611,46 @@
       <c r="M50" t="n">
         <v>1</v>
       </c>
-      <c r="N50" t="n">
-        <v>10456</v>
-      </c>
       <c r="O50" t="n">
         <v>18</v>
       </c>
       <c r="P50" t="n">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="Q50" t="n">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="R50" t="n">
         <v>4</v>
       </c>
       <c r="S50" t="n">
-        <v>191</v>
+        <v>56</v>
       </c>
       <c r="T50" t="n">
-        <v>4191</v>
+        <v>4056</v>
       </c>
       <c r="U50" t="n">
         <v>1</v>
       </c>
-      <c r="V50" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="W50" t="n">
-        <v>6000000</v>
-      </c>
       <c r="X50" t="n">
-        <v>6000000</v>
+        <v>200000</v>
       </c>
       <c r="Y50" t="n">
         <v>0</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>MONITORAMENTO HIDROMETEOROLOGICO</t>
+          <t>RECUPERAÇÃO AMBIENTAL</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>FORTALECIMENTO DA POLÍTICA ESTADUAL DE RECURSOS HÍDRICOS</t>
+          <t>PROTEÇÃO DAS ÁREAS AMBIENTALMENTE CONSERVADAS, DA FAUNA E DA BIODIVERSIDADE FLORESTAL</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -6190,37 +5660,34 @@
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>INSTRUMENTO A SER CRIADO</t>
+          <t>9445719</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>Ampliação, modernização e equipagem da rede meteorológica, rede hidrológica e Sala de Situação para eventos hidrológicos críticos, de forma a aprimorar a capacidade do Sistema Estadual de Meio Ambiente (SISEMA) de acompanhar a recuperação da Bacia Hidrográfica do Rio Doce vis-à-vis riscos decorrentes de eventos climáticos extremos.</t>
+          <t>RECUPERAÇÃO DA VEGETAÇÃO NATIVA NA BACIA HIDROGRÁFICA DO RIO DOCE, COM PRIORIDADE ÀS ÁREAS DE MATA RIPÁRIA, POR MEIO DE AÇÕES DE REFLORESTAMENTO, PAGAMENTO DE SERVIÇOS AMBIENTAIS, MAPEAMENTO DO USO DE SOLO E INVESTIMENTO TECNOLÓGICO PARA MONITORAMENTO DA VEGETAÇÃO NATIVA E SUA RECUPERAÇÃO</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Ampliação, modernização e equipagem da rede meteorológica, rede hidrológica e Sala de Situação para eventos hidrológicos críticos, de forma a aprimorar a capacidade do Sistema Estadual de Meio Ambiente (SISEMA) de acompanhar a recuperação da Bacia Hidrográfica do Rio Doce vis-à-vis riscos decorrentes de eventos climáticos extremos.</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9445719 - RECUPERAÇÃO DA VEGETAÇÃO NATIVA NA BACIA HIDROGRÁFICA DO RIO DOCE, COM PRIORIDADE ÀS ÁREAS DE MATA RIPÁRIA, POR MEIO DE AÇÕES DE REFLORESTAMENTO, PAGAMENTO DE SERVIÇOS AMBIENTAIS, MAPEAMENTO DO USO DE SOLO E INVESTIMENTO TECNOLÓGICO PARA MONITORAMENTO DA VEGETAÇÃO NATIVA E SUA RECUPERAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B51" t="n">
         <v>1370</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IGAM</t>
         </is>
       </c>
       <c r="D51" t="n">
         <v>3</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0</v>
       </c>
       <c r="F51" t="n">
         <v>2241</v>
@@ -6237,10 +5704,10 @@
         <v>3</v>
       </c>
       <c r="J51" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="K51" t="n">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="L51" t="n">
         <v>80</v>
@@ -6248,9 +5715,6 @@
       <c r="M51" t="n">
         <v>1</v>
       </c>
-      <c r="N51" t="n">
-        <v>10456</v>
-      </c>
       <c r="O51" t="n">
         <v>18</v>
       </c>
@@ -6272,14 +5736,8 @@
       <c r="U51" t="n">
         <v>1</v>
       </c>
-      <c r="V51" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="W51" t="n">
-        <v>10000000</v>
-      </c>
       <c r="X51" t="n">
-        <v>10000000</v>
+        <v>15000000</v>
       </c>
       <c r="Y51" t="n">
         <v>0</v>
@@ -6296,7 +5754,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -6306,37 +5764,34 @@
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>INSTRUMENTO A SER CRIADO</t>
+          <t>9480440</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>Ampliação, modernização e equipagem da rede meteorológica, rede hidrológica e Sala de Situação para eventos hidrológicos críticos, de forma a aprimorar a capacidade do Sistema Estadual de Meio Ambiente (SISEMA) de acompanhar a recuperação da Bacia Hidrográfica do Rio Doce vis-à-vis riscos decorrentes de eventos climáticos extremos.</t>
+          <t>AMPLIAÇÃO, MODERNIZAÇÃO E EQUIPAGEM DA REDE METEOROLÓGICA, REDE HIDROLÓGICA E SALA DE SITUAÇÃO PARA EVENTOS HIDROLÓGICOS CRÍTICOS, DE FORMA A APRIMORAR A CAPACIDADE DO SISTEMA ESTADUAL DE MEIO AMBIENTE (SISEMA) DE ACOMPANHAR A RECUPERAÇÃO DA BACIA HIDROGRÁFICA DO RIO DOCE VIS-À-VIS RISCOS DECORRENTES DE EVENTOS CLIMÁTICOS EXTREMOS.</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Ampliação, modernização e equipagem da rede meteorológica, rede hidrológica e Sala de Situação para eventos hidrológicos críticos, de forma a aprimorar a capacidade do Sistema Estadual de Meio Ambiente (SISEMA) de acompanhar a recuperação da Bacia Hidrográfica do Rio Doce vis-à-vis riscos decorrentes de eventos climáticos extremos.</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9480440 - AMPLIAÇÃO, MODERNIZAÇÃO E EQUIPAGEM DA REDE METEOROLÓGICA, REDE HIDROLÓGICA E SALA DE SITUAÇÃO PARA EVENTOS HIDROLÓGICOS CRÍTICOS, DE FORMA A APRIMORAR A CAPACIDADE DO SISTEMA ESTADUAL DE MEIO AMBIENTE (SISEMA) DE ACOMPANHAR A RECUPERAÇÃO DA BACIA HIDROGRÁFICA DO RIO DOCE VIS-À-VIS RISCOS DECORRENTES DE EVENTOS CLIMÁTICOS EXTREMOS.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B52" t="n">
         <v>1370</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - IGAM</t>
         </is>
       </c>
       <c r="D52" t="n">
         <v>3</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0</v>
       </c>
       <c r="F52" t="n">
         <v>2241</v>
@@ -6364,9 +5819,6 @@
       <c r="M52" t="n">
         <v>1</v>
       </c>
-      <c r="N52" t="n">
-        <v>10456</v>
-      </c>
       <c r="O52" t="n">
         <v>18</v>
       </c>
@@ -6380,29 +5832,23 @@
         <v>4</v>
       </c>
       <c r="S52" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="T52" t="n">
-        <v>4191</v>
+        <v>4192</v>
       </c>
       <c r="U52" t="n">
         <v>1</v>
       </c>
-      <c r="V52" t="n">
-        <v>5335000</v>
-      </c>
-      <c r="W52" t="n">
-        <v>5335000</v>
-      </c>
       <c r="X52" t="n">
-        <v>5335000</v>
+        <v>1100000</v>
       </c>
       <c r="Y52" t="n">
         <v>0</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>MONITORAMENTO HIDROMETEOROLOGICO</t>
+          <t>SEGURANÇA DE BARRAGENS</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6412,7 +5858,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -6422,57 +5868,54 @@
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>INSTRUMENTO A SER CRIADO</t>
+          <t>9480693</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>Ampliação, modernização e equipagem da rede meteorológica, rede hidrológica e Sala de Situação para eventos hidrológicos críticos, de forma a aprimorar a capacidade do Sistema Estadual de Meio Ambiente (SISEMA) de acompanhar a recuperação da Bacia Hidrográfica do Rio Doce vis-à-vis riscos decorrentes de eventos climáticos extremos.</t>
+          <t>MELHORIA NA CAPACIDADE ESTADUAL FISCALIZATÓRIA DE BARRAGENS NAS ESTRUTURAS LOCALIZADAS NA EXTENSÃO TERRITORIAL DA BACIA HIDROGRÁFICA DO RIO DOCE: AQUISIÇÃO DE EQUIPAMENTOS FÍSICOS E TECNOLÓGICOS, CONTRATAÇÃO DE SERVIÇOS DE CONSULTORIA</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Ampliação, modernização e equipagem da rede meteorológica, rede hidrológica e Sala de Situação para eventos hidrológicos críticos, de forma a aprimorar a capacidade do Sistema Estadual de Meio Ambiente (SISEMA) de acompanhar a recuperação da Bacia Hidrográfica do Rio Doce vis-à-vis riscos decorrentes de eventos climáticos extremos.</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9480693 - MELHORIA NA CAPACIDADE ESTADUAL FISCALIZATÓRIA DE BARRAGENS NAS ESTRUTURAS LOCALIZADAS NA EXTENSÃO TERRITORIAL DA BACIA HIDROGRÁFICA DO RIO DOCE: AQUISIÇÃO DE EQUIPAMENTOS FÍSICOS E TECNOLÓGICOS, CONTRATAÇÃO DE SERVIÇOS DE CONSULTORIA</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B53" t="n">
-        <v>1370</v>
+        <v>1480</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
         </is>
       </c>
       <c r="D53" t="n">
         <v>3</v>
       </c>
-      <c r="E53" t="n">
-        <v>0</v>
-      </c>
       <c r="F53" t="n">
-        <v>2241</v>
+        <v>1481</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE GESTÃO DAS ÁGUAS - IGAM</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J53" t="n">
         <v>90</v>
       </c>
       <c r="K53" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="L53" t="n">
         <v>80</v>
@@ -6480,55 +5923,46 @@
       <c r="M53" t="n">
         <v>1</v>
       </c>
-      <c r="N53" t="n">
-        <v>10456</v>
-      </c>
       <c r="O53" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="P53" t="n">
-        <v>544</v>
+        <v>363</v>
       </c>
       <c r="Q53" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="R53" t="n">
         <v>4</v>
       </c>
       <c r="S53" t="n">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="T53" t="n">
-        <v>4191</v>
+        <v>4158</v>
       </c>
       <c r="U53" t="n">
         <v>1</v>
       </c>
-      <c r="V53" t="n">
-        <v>35000000</v>
-      </c>
-      <c r="W53" t="n">
-        <v>35000000</v>
-      </c>
       <c r="X53" t="n">
-        <v>35000000</v>
+        <v>1890827</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>MONITORAMENTO HIDROMETEOROLOGICO</t>
+          <t>QUALIFICAÇÃO PROFISSIONAL</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>FORTALECIMENTO DA POLÍTICA ESTADUAL DE RECURSOS HÍDRICOS</t>
+          <t>REDE DE DESENVOLVIMENTO DA EDUCAÇÃO PROFISSIONAL</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -6538,57 +5972,54 @@
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>INSTRUMENTO A SER CRIADO</t>
+          <t>9456621</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>Ampliação, modernização e equipagem da rede meteorológica, rede hidrológica e Sala de Situação para eventos hidrológicos críticos, de forma a aprimorar a capacidade do Sistema Estadual de Meio Ambiente (SISEMA) de acompanhar a recuperação da Bacia Hidrográfica do Rio Doce vis-à-vis riscos decorrentes de eventos climáticos extremos.</t>
+          <t>OFERTA DE CURSOS DE QUALIFICAÇÃO PROFISSIONAL A PARTIR DE ESTUDO DE DEMANDAS DO MERCADO DE TRABALHO</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Ampliação, modernização e equipagem da rede meteorológica, rede hidrológica e Sala de Situação para eventos hidrológicos críticos, de forma a aprimorar a capacidade do Sistema Estadual de Meio Ambiente (SISEMA) de acompanhar a recuperação da Bacia Hidrográfica do Rio Doce vis-à-vis riscos decorrentes de eventos climáticos extremos.</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9456621 - OFERTA DE CURSOS DE QUALIFICAÇÃO PROFISSIONAL A PARTIR DE ESTUDO DE DEMANDAS DO MERCADO DE TRABALHO</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B54" t="n">
-        <v>1370</v>
+        <v>1480</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL - SEMAD</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
         </is>
       </c>
       <c r="D54" t="n">
         <v>3</v>
       </c>
-      <c r="E54" t="n">
-        <v>0</v>
-      </c>
       <c r="F54" t="n">
-        <v>2241</v>
+        <v>1481</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE GESTÃO DAS ÁGUAS - IGAM</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J54" t="n">
         <v>90</v>
       </c>
       <c r="K54" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L54" t="n">
         <v>80</v>
@@ -6596,55 +6027,46 @@
       <c r="M54" t="n">
         <v>1</v>
       </c>
-      <c r="N54" t="n">
-        <v>10457</v>
-      </c>
       <c r="O54" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="P54" t="n">
-        <v>544</v>
+        <v>363</v>
       </c>
       <c r="Q54" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="R54" t="n">
         <v>4</v>
       </c>
       <c r="S54" t="n">
-        <v>192</v>
+        <v>158</v>
       </c>
       <c r="T54" t="n">
-        <v>4192</v>
+        <v>4158</v>
       </c>
       <c r="U54" t="n">
         <v>1</v>
       </c>
-      <c r="V54" t="n">
-        <v>1686667</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1686667</v>
-      </c>
       <c r="X54" t="n">
-        <v>1686667</v>
+        <v>810354</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>SEGURANÇA DE BARRAGENS</t>
+          <t>QUALIFICAÇÃO PROFISSIONAL</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>FORTALECIMENTO DA POLÍTICA ESTADUAL DE RECURSOS HÍDRICOS</t>
+          <t>REDE DE DESENVOLVIMENTO DA EDUCAÇÃO PROFISSIONAL</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -6654,44 +6076,41 @@
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>INSTRUMENTO A SER CRIADO</t>
+          <t>9456621</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>Melhoria na capacidade estadual fiscalizatória de barragens nas estruturas localizadas na extensão territorial da Bacia Hidrográfica do Rio Doce: aquisição de equipamentos físicos e tecnológicos, contratação de serviços de consultoria</t>
+          <t>OFERTA DE CURSOS DE QUALIFICAÇÃO PROFISSIONAL A PARTIR DE ESTUDO DE DEMANDAS DO MERCADO DE TRABALHO</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - INSTRUMENTO A SER CRIADO - Melhoria na capacidade estadual fiscalizatória de barragens nas estruturas localizadas na extensão territorial da Bacia Hidrográfica do Rio Doce: aquisição de equipamentos físicos e tecnológicos, contratação de serviços de consultoria</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9456621 - OFERTA DE CURSOS DE QUALIFICAÇÃO PROFISSIONAL A PARTIR DE ESTUDO DE DEMANDAS DO MERCADO DE TRABALHO</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B55" t="n">
         <v>1480</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - FEAS</t>
         </is>
       </c>
       <c r="D55" t="n">
         <v>3</v>
       </c>
-      <c r="E55" t="n">
-        <v>0</v>
-      </c>
       <c r="F55" t="n">
-        <v>1481</v>
+        <v>4251</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+          <t>FUNDO ESTADUAL DE ASSISTÊNCIA SOCIAL - FEAS</t>
         </is>
       </c>
       <c r="H55" t="n">
@@ -6701,10 +6120,10 @@
         <v>3</v>
       </c>
       <c r="J55" t="n">
-        <v>90</v>
+        <v>41</v>
       </c>
       <c r="K55" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="L55" t="n">
         <v>80</v>
@@ -6712,55 +6131,46 @@
       <c r="M55" t="n">
         <v>1</v>
       </c>
-      <c r="N55" t="n">
-        <v>10419</v>
-      </c>
       <c r="O55" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P55" t="n">
-        <v>334</v>
+        <v>244</v>
       </c>
       <c r="Q55" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="R55" t="n">
         <v>4</v>
       </c>
       <c r="S55" t="n">
-        <v>154</v>
+        <v>402</v>
       </c>
       <c r="T55" t="n">
-        <v>4154</v>
+        <v>4402</v>
       </c>
       <c r="U55" t="n">
         <v>1</v>
       </c>
-      <c r="V55" t="n">
-        <v>220000</v>
-      </c>
-      <c r="W55" t="n">
-        <v>220000</v>
-      </c>
       <c r="X55" t="n">
-        <v>220000</v>
+        <v>15850920</v>
       </c>
       <c r="Y55" t="n">
         <v>0</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>FOMENTO PARA ECONOMIA POPULAR SOLIDÁRIA E PROMOÇÃO DA INCLUSÃO PRODUTIVA</t>
+          <t>FORTALECIMENTO DO SUAS NA BACIA DO RIO DOCE</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>POLÍTICAS DE TRABALHO E EMPREGO</t>
+          <t>FORTALECIMENTO DO SISTEMA ÚNICO DE ASSISTÊNCIA SOCIAL - SUAS</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -6768,44 +6178,43 @@
           <t>ANEXO 12</t>
         </is>
       </c>
-      <c r="AD55" t="n">
-        <v>9456618</v>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>9445718</t>
+        </is>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>Disponibilização de microcrédito para financiamento de atividades produtivas, podendo ter o apoio de agentes de crédito facilitadores</t>
+          <t>FORTALECIMENTO DO ATENDIMENTO DA REDE SOCIOASSISTENCIAL COM EXECUÇÃO DE UM PLANO DE MELHORIAS, QUE INCLUA, PREFERENCIALMENTE, CONSTRUÇÃO E REFORMA DE UNIDADES DO CENTRO DE REFERÊNCIA DE ASSISTÊNCIA SOCIAL (CRAS) E CENTRO DE REFERÊNCIA ESPECIALIZADO DE ASSISTÊNCIA SOCIAL (CREAS), CONTRATAÇÃO DE EQUIPE TÉCNICA E AQUISIÇÃO DE MATERIAL DE CONSUMO DE ACORDO COM DETALHAMENTO A SER CONSTRUÍDO PRIORITARIAMENTE</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456618 - Disponibilização de microcrédito para financiamento de atividades produtivas, podendo ter o apoio de agentes de crédito facilitadores</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9445718 - FORTALECIMENTO DO ATENDIMENTO DA REDE SOCIOASSISTENCIAL COM EXECUÇÃO DE UM PLANO DE MELHORIAS, QUE INCLUA, PREFERENCIALMENTE, CONSTRUÇÃO E REFORMA DE UNIDADES DO CENTRO DE REFERÊNCIA DE ASSISTÊNCIA SOCIAL (CRAS) E CENTRO DE REFERÊNCIA ESPECIALIZADO DE ASSISTÊNCIA SOCIAL (CREAS), CONTRATAÇÃO DE EQUIPE TÉCNICA E AQUISIÇÃO DE MATERIAL DE CONSUMO DE ACORDO COM DETALHAMENTO A SER CONSTRUÍDO PRIORITARIAMENTE</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B56" t="n">
         <v>1480</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - FEAS</t>
         </is>
       </c>
       <c r="D56" t="n">
         <v>3</v>
       </c>
-      <c r="E56" t="n">
-        <v>0</v>
-      </c>
       <c r="F56" t="n">
-        <v>1481</v>
+        <v>4251</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+          <t>FUNDO ESTADUAL DE ASSISTÊNCIA SOCIAL - FEAS</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -6818,7 +6227,7 @@
         <v>90</v>
       </c>
       <c r="K56" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="L56" t="n">
         <v>80</v>
@@ -6826,55 +6235,46 @@
       <c r="M56" t="n">
         <v>1</v>
       </c>
-      <c r="N56" t="n">
-        <v>10419</v>
-      </c>
       <c r="O56" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P56" t="n">
-        <v>334</v>
+        <v>244</v>
       </c>
       <c r="Q56" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="R56" t="n">
         <v>4</v>
       </c>
       <c r="S56" t="n">
-        <v>154</v>
+        <v>402</v>
       </c>
       <c r="T56" t="n">
-        <v>4154</v>
+        <v>4402</v>
       </c>
       <c r="U56" t="n">
         <v>1</v>
       </c>
-      <c r="V56" t="n">
-        <v>6878500</v>
-      </c>
-      <c r="W56" t="n">
-        <v>6878500</v>
-      </c>
       <c r="X56" t="n">
-        <v>6878500</v>
+        <v>15082</v>
       </c>
       <c r="Y56" t="n">
         <v>0</v>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>FOMENTO PARA ECONOMIA POPULAR SOLIDÁRIA E PROMOÇÃO DA INCLUSÃO PRODUTIVA</t>
+          <t>FORTALECIMENTO DO SUAS NA BACIA DO RIO DOCE</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>POLÍTICAS DE TRABALHO E EMPREGO</t>
+          <t>FORTALECIMENTO DO SISTEMA ÚNICO DE ASSISTÊNCIA SOCIAL - SUAS</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -6882,44 +6282,43 @@
           <t>ANEXO 12</t>
         </is>
       </c>
-      <c r="AD56" t="n">
-        <v>9456618</v>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>9468055</t>
+        </is>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>Disponibilização de microcrédito para financiamento de atividades produtivas, podendo ter o apoio de agentes de crédito facilitadores</t>
+          <t>SUPORTE GERENCIAL, ADMINISTRATIVO, TECNOLÓGICO E DE COMUNICAÇÃO SOCIAL À IMPLEMENTAÇÃO</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456618 - Disponibilização de microcrédito para financiamento de atividades produtivas, podendo ter o apoio de agentes de crédito facilitadores</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9468055 - SUPORTE GERENCIAL, ADMINISTRATIVO, TECNOLÓGICO E DE COMUNICAÇÃO SOCIAL À IMPLEMENTAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B57" t="n">
         <v>1480</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - FEAS</t>
         </is>
       </c>
       <c r="D57" t="n">
         <v>3</v>
       </c>
-      <c r="E57" t="n">
-        <v>0</v>
-      </c>
       <c r="F57" t="n">
-        <v>1481</v>
+        <v>4251</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+          <t>FUNDO ESTADUAL DE ASSISTÊNCIA SOCIAL - FEAS</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -6940,55 +6339,46 @@
       <c r="M57" t="n">
         <v>1</v>
       </c>
-      <c r="N57" t="n">
-        <v>10423</v>
-      </c>
       <c r="O57" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P57" t="n">
-        <v>363</v>
+        <v>244</v>
       </c>
       <c r="Q57" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="R57" t="n">
         <v>4</v>
       </c>
       <c r="S57" t="n">
-        <v>158</v>
+        <v>402</v>
       </c>
       <c r="T57" t="n">
-        <v>4158</v>
+        <v>4402</v>
       </c>
       <c r="U57" t="n">
         <v>1</v>
       </c>
-      <c r="V57" t="n">
-        <v>440000</v>
-      </c>
-      <c r="W57" t="n">
-        <v>440000</v>
-      </c>
       <c r="X57" t="n">
-        <v>440000</v>
+        <v>1479414</v>
       </c>
       <c r="Y57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>QUALIFICAÇÃO PROFISSIONAL</t>
+          <t>FORTALECIMENTO DO SUAS NA BACIA DO RIO DOCE</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>REDE DE DESENVOLVIMENTO DA EDUCAÇÃO PROFISSIONAL</t>
+          <t>FORTALECIMENTO DO SISTEMA ÚNICO DE ASSISTÊNCIA SOCIAL - SUAS</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -6996,57 +6386,56 @@
           <t>ANEXO 12</t>
         </is>
       </c>
-      <c r="AD57" t="n">
-        <v>9456621</v>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>9468055</t>
+        </is>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>Oferta de cursos de qualificação profissional a partir de estudo de demandas do mercado de trabalho</t>
+          <t>SUPORTE GERENCIAL, ADMINISTRATIVO, TECNOLÓGICO E DE COMUNICAÇÃO SOCIAL À IMPLEMENTAÇÃO</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456621 - Oferta de cursos de qualificação profissional a partir de estudo de demandas do mercado de trabalho</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9468055 - SUPORTE GERENCIAL, ADMINISTRATIVO, TECNOLÓGICO E DE COMUNICAÇÃO SOCIAL À IMPLEMENTAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B58" t="n">
         <v>1480</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - FEAS</t>
         </is>
       </c>
       <c r="D58" t="n">
         <v>3</v>
       </c>
-      <c r="E58" t="n">
-        <v>0</v>
-      </c>
       <c r="F58" t="n">
-        <v>1481</v>
+        <v>4251</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+          <t>FUNDO ESTADUAL DE ASSISTÊNCIA SOCIAL - FEAS</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J58" t="n">
-        <v>90</v>
+        <v>41</v>
       </c>
       <c r="K58" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L58" t="n">
         <v>80</v>
@@ -7054,55 +6443,46 @@
       <c r="M58" t="n">
         <v>1</v>
       </c>
-      <c r="N58" t="n">
-        <v>10423</v>
-      </c>
       <c r="O58" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P58" t="n">
-        <v>363</v>
+        <v>244</v>
       </c>
       <c r="Q58" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="R58" t="n">
         <v>4</v>
       </c>
       <c r="S58" t="n">
-        <v>158</v>
+        <v>402</v>
       </c>
       <c r="T58" t="n">
-        <v>4158</v>
+        <v>4402</v>
       </c>
       <c r="U58" t="n">
         <v>1</v>
       </c>
-      <c r="V58" t="n">
-        <v>2709019</v>
-      </c>
-      <c r="W58" t="n">
-        <v>2709019</v>
-      </c>
       <c r="X58" t="n">
-        <v>2709019</v>
+        <v>20000000</v>
       </c>
       <c r="Y58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>QUALIFICAÇÃO PROFISSIONAL</t>
+          <t>FORTALECIMENTO DO SUAS NA BACIA DO RIO DOCE</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>REDE DE DESENVOLVIMENTO DA EDUCAÇÃO PROFISSIONAL</t>
+          <t>FORTALECIMENTO DO SISTEMA ÚNICO DE ASSISTÊNCIA SOCIAL - SUAS</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -7110,37 +6490,36 @@
           <t>ANEXO 12</t>
         </is>
       </c>
-      <c r="AD58" t="n">
-        <v>9456621</v>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>9445718</t>
+        </is>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>Oferta de cursos de qualificação profissional a partir de estudo de demandas do mercado de trabalho</t>
+          <t>FORTALECIMENTO DO ATENDIMENTO DA REDE SOCIOASSISTENCIAL COM EXECUÇÃO DE UM PLANO DE MELHORIAS, QUE INCLUA, PREFERENCIALMENTE, CONSTRUÇÃO E REFORMA DE UNIDADES DO CENTRO DE REFERÊNCIA DE ASSISTÊNCIA SOCIAL (CRAS) E CENTRO DE REFERÊNCIA ESPECIALIZADO DE ASSISTÊNCIA SOCIAL (CREAS), CONTRATAÇÃO DE EQUIPE TÉCNICA E AQUISIÇÃO DE MATERIAL DE CONSUMO DE ACORDO COM DETALHAMENTO A SER CONSTRUÍDO PRIORITARIAMENTE</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9456621 - Oferta de cursos de qualificação profissional a partir de estudo de demandas do mercado de trabalho</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9445718 - FORTALECIMENTO DO ATENDIMENTO DA REDE SOCIOASSISTENCIAL COM EXECUÇÃO DE UM PLANO DE MELHORIAS, QUE INCLUA, PREFERENCIALMENTE, CONSTRUÇÃO E REFORMA DE UNIDADES DO CENTRO DE REFERÊNCIA DE ASSISTÊNCIA SOCIAL (CRAS) E CENTRO DE REFERÊNCIA ESPECIALIZADO DE ASSISTÊNCIA SOCIAL (CREAS), CONTRATAÇÃO DE EQUIPE TÉCNICA E AQUISIÇÃO DE MATERIAL DE CONSUMO DE ACORDO COM DETALHAMENTO A SER CONSTRUÍDO PRIORITARIAMENTE</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B59" t="n">
         <v>1480</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - FEAS</t>
         </is>
       </c>
       <c r="D59" t="n">
         <v>3</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0</v>
       </c>
       <c r="F59" t="n">
         <v>4251</v>
@@ -7157,10 +6536,10 @@
         <v>3</v>
       </c>
       <c r="J59" t="n">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="K59" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="L59" t="n">
         <v>80</v>
@@ -7168,9 +6547,6 @@
       <c r="M59" t="n">
         <v>1</v>
       </c>
-      <c r="N59" t="n">
-        <v>11267</v>
-      </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
@@ -7184,29 +6560,23 @@
         <v>4</v>
       </c>
       <c r="S59" t="n">
-        <v>402</v>
+        <v>433</v>
       </c>
       <c r="T59" t="n">
-        <v>4402</v>
+        <v>4433</v>
       </c>
       <c r="U59" t="n">
         <v>1</v>
       </c>
-      <c r="V59" t="n">
-        <v>5952959</v>
-      </c>
-      <c r="W59" t="n">
-        <v>5952959</v>
-      </c>
       <c r="X59" t="n">
-        <v>5952959</v>
+        <v>1238033</v>
       </c>
       <c r="Y59" t="n">
         <v>0</v>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>FORTALECIMENTO DO SUAS NA BACIA DO RIO DOCE</t>
+          <t>GESTÃO DA POLÍTICA ESTADUAL DE ASSISTÊNCIA SOCIAL</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7216,65 +6586,64 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>ANEXO 12</t>
-        </is>
-      </c>
-      <c r="AD59" t="n">
-        <v>9445718</v>
+          <t>ANEXO 07</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>9445684</t>
+        </is>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>Fortalecimento do atendimento da rede socioassistencial com execução de um plano de melhorias, que inclua, preferencialmente, construção e reforma de unidades do Centro de Referência de Assistência Social (CRAS) e Centro de Referência Especializado de Assistência Social (CREAS), contratação de equipe técnica e aquisição de material de consumo de acordo com detalhamento a ser construído prioritariamente</t>
+          <t>FORTALECIMENTO DO SISTEMA ÚNICO DE ASSISTÊNCIA SOCIAL (SUAS)</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9445718 - Fortalecimento do atendimento da rede socioassistencial com execução de um plano de melhorias, que inclua, preferencialmente, construção e reforma de unidades do Centro de Referência de Assistência Social (CRAS) e Centro de Referência Especializado de Assistência Social (CREAS), contratação de equipe técnica e aquisição de material de consumo de acordo com detalhamento a ser construído prioritariamente</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 07 - 9445684 - FORTALECIMENTO DO SISTEMA ÚNICO DE ASSISTÊNCIA SOCIAL (SUAS)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B60" t="n">
-        <v>1480</v>
+        <v>1500</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
         </is>
       </c>
       <c r="D60" t="n">
         <v>3</v>
       </c>
-      <c r="E60" t="n">
-        <v>0</v>
-      </c>
       <c r="F60" t="n">
-        <v>4251</v>
+        <v>1501</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE ASSISTÊNCIA SOCIAL - FEAS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J60" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="K60" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="L60" t="n">
         <v>80</v>
@@ -7282,55 +6651,46 @@
       <c r="M60" t="n">
         <v>1</v>
       </c>
-      <c r="N60" t="n">
-        <v>11267</v>
-      </c>
       <c r="O60" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P60" t="n">
-        <v>244</v>
+        <v>122</v>
       </c>
       <c r="Q60" t="n">
-        <v>71</v>
+        <v>155</v>
       </c>
       <c r="R60" t="n">
         <v>4</v>
       </c>
       <c r="S60" t="n">
-        <v>402</v>
+        <v>461</v>
       </c>
       <c r="T60" t="n">
-        <v>4402</v>
+        <v>4461</v>
       </c>
       <c r="U60" t="n">
         <v>1</v>
       </c>
-      <c r="V60" t="n">
-        <v>27847404</v>
-      </c>
-      <c r="W60" t="n">
-        <v>27847404</v>
-      </c>
       <c r="X60" t="n">
-        <v>27847404</v>
+        <v>120000</v>
       </c>
       <c r="Y60" t="n">
         <v>0</v>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>FORTALECIMENTO DO SUAS NA BACIA DO RIO DOCE</t>
+          <t>RECUPERAÇÃO E COMPENSAÇÃO DOS DANOS EM FUNÇÃO DO DESASTRE MINERÁRIO DA SAMARCO EM MARIANA</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>FORTALECIMENTO DO SISTEMA ÚNICO DE ASSISTÊNCIA SOCIAL - SUAS</t>
+          <t>REPARAÇÃO DOS DANOS DOS ROMPIMENTOS EM BRUMADINHO E MARIANA</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -7338,44 +6698,43 @@
           <t>ANEXO 12</t>
         </is>
       </c>
-      <c r="AD60" t="n">
-        <v>9445718</v>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>9468055</t>
+        </is>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>Fortalecimento do atendimento da rede socioassistencial com execução de um plano de melhorias, que inclua, preferencialmente, construção e reforma de unidades do Centro de Referência de Assistência Social (CRAS) e Centro de Referência Especializado de Assistência Social (CREAS), contratação de equipe técnica e aquisição de material de consumo de acordo com detalhamento a ser construído prioritariamente</t>
+          <t>SUPORTE GERENCIAL, ADMINISTRATIVO, TECNOLÓGICO E DE COMUNICAÇÃO SOCIAL À IMPLEMENTAÇÃO DAS INICIATIVAS LISTA 3</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9445718 - Fortalecimento do atendimento da rede socioassistencial com execução de um plano de melhorias, que inclua, preferencialmente, construção e reforma de unidades do Centro de Referência de Assistência Social (CRAS) e Centro de Referência Especializado de Assistência Social (CREAS), contratação de equipe técnica e aquisição de material de consumo de acordo com detalhamento a ser construído prioritariamente</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9468055 - SUPORTE GERENCIAL, ADMINISTRATIVO, TECNOLÓGICO E DE COMUNICAÇÃO SOCIAL À IMPLEMENTAÇÃO DAS INICIATIVAS LISTA 3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B61" t="n">
-        <v>1480</v>
+        <v>1500</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
         </is>
       </c>
       <c r="D61" t="n">
         <v>3</v>
       </c>
-      <c r="E61" t="n">
-        <v>0</v>
-      </c>
       <c r="F61" t="n">
-        <v>4251</v>
+        <v>1501</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE ASSISTÊNCIA SOCIAL - FEAS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -7388,7 +6747,7 @@
         <v>90</v>
       </c>
       <c r="K61" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="L61" t="n">
         <v>80</v>
@@ -7396,79 +6755,72 @@
       <c r="M61" t="n">
         <v>1</v>
       </c>
-      <c r="N61" t="n">
-        <v>10777</v>
-      </c>
       <c r="O61" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P61" t="n">
-        <v>244</v>
+        <v>122</v>
       </c>
       <c r="Q61" t="n">
-        <v>71</v>
+        <v>155</v>
       </c>
       <c r="R61" t="n">
         <v>4</v>
       </c>
       <c r="S61" t="n">
-        <v>433</v>
+        <v>461</v>
       </c>
       <c r="T61" t="n">
-        <v>4433</v>
+        <v>4461</v>
       </c>
       <c r="U61" t="n">
         <v>1</v>
       </c>
-      <c r="V61" t="n">
-        <v>1600000</v>
-      </c>
-      <c r="W61" t="n">
-        <v>1600000</v>
-      </c>
       <c r="X61" t="n">
-        <v>1600000</v>
+        <v>110000</v>
       </c>
       <c r="Y61" t="n">
         <v>0</v>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>GESTÃO DA POLÍTICA ESTADUAL DE ASSISTÊNCIA SOCIAL</t>
+          <t>RECUPERAÇÃO E COMPENSAÇÃO DOS DANOS EM FUNÇÃO DO DESASTRE MINERÁRIO DA SAMARCO EM MARIANA</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>FORTALECIMENTO DO SISTEMA ÚNICO DE ASSISTÊNCIA SOCIAL - SUAS</t>
+          <t>REPARAÇÃO DOS DANOS DOS ROMPIMENTOS EM BRUMADINHO E MARIANA</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>ANEXO 07</t>
-        </is>
-      </c>
-      <c r="AD61" t="n">
-        <v>9445684</v>
+          <t>ANEXO 12</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>9468055</t>
+        </is>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>Fortalecimento do Sistema Único de Assistência Social (SUAS)</t>
+          <t>SUPORTE GERENCIAL, ADMINISTRATIVO, TECNOLÓGICO E DE COMUNICAÇÃO SOCIAL À IMPLEMENTAÇÃO DAS INICIATIVAS LISTA 3</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 07 - 9445684 - Fortalecimento do Sistema Único de Assistência Social (SUAS)</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9468055 - SUPORTE GERENCIAL, ADMINISTRATIVO, TECNOLÓGICO E DE COMUNICAÇÃO SOCIAL À IMPLEMENTAÇÃO DAS INICIATIVAS LISTA 3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B62" t="n">
         <v>1500</v>
@@ -7481,9 +6833,6 @@
       <c r="D62" t="n">
         <v>3</v>
       </c>
-      <c r="E62" t="n">
-        <v>0</v>
-      </c>
       <c r="F62" t="n">
         <v>1501</v>
       </c>
@@ -7496,13 +6845,13 @@
         <v>3</v>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J62" t="n">
         <v>90</v>
       </c>
       <c r="K62" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="L62" t="n">
         <v>80</v>
@@ -7510,9 +6859,6 @@
       <c r="M62" t="n">
         <v>1</v>
       </c>
-      <c r="N62" t="n">
-        <v>10819</v>
-      </c>
       <c r="O62" t="n">
         <v>4</v>
       </c>
@@ -7534,14 +6880,8 @@
       <c r="U62" t="n">
         <v>1</v>
       </c>
-      <c r="V62" t="n">
-        <v>465500</v>
-      </c>
-      <c r="W62" t="n">
-        <v>465500</v>
-      </c>
       <c r="X62" t="n">
-        <v>465500</v>
+        <v>8077861</v>
       </c>
       <c r="Y62" t="n">
         <v>0</v>
@@ -7558,7 +6898,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -7566,23 +6906,25 @@
           <t>ANEXO 12</t>
         </is>
       </c>
-      <c r="AD62" t="n">
-        <v>9468055</v>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>9468055</t>
+        </is>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas Lista 3</t>
+          <t>SUPORTE GERENCIAL, ADMINISTRATIVO, TECNOLÓGICO E DE COMUNICAÇÃO SOCIAL À IMPLEMENTAÇÃO DAS INICIATIVAS LISTA 3</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9468055 - Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas Lista 3</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9468055 - SUPORTE GERENCIAL, ADMINISTRATIVO, TECNOLÓGICO E DE COMUNICAÇÃO SOCIAL À IMPLEMENTAÇÃO DAS INICIATIVAS LISTA 3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B63" t="n">
         <v>1500</v>
@@ -7595,9 +6937,6 @@
       <c r="D63" t="n">
         <v>3</v>
       </c>
-      <c r="E63" t="n">
-        <v>0</v>
-      </c>
       <c r="F63" t="n">
         <v>1501</v>
       </c>
@@ -7610,22 +6949,19 @@
         <v>3</v>
       </c>
       <c r="I63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>90</v>
       </c>
       <c r="K63" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L63" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="M63" t="n">
         <v>1</v>
-      </c>
-      <c r="N63" t="n">
-        <v>10819</v>
       </c>
       <c r="O63" t="n">
         <v>4</v>
@@ -7640,29 +6976,23 @@
         <v>4</v>
       </c>
       <c r="S63" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="T63" t="n">
-        <v>4461</v>
+        <v>4462</v>
       </c>
       <c r="U63" t="n">
         <v>1</v>
       </c>
-      <c r="V63" t="n">
-        <v>125000</v>
-      </c>
-      <c r="W63" t="n">
-        <v>125000</v>
-      </c>
       <c r="X63" t="n">
-        <v>125000</v>
+        <v>1000</v>
       </c>
       <c r="Y63" t="n">
         <v>0</v>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO E COMPENSAÇÃO DOS DANOS EM FUNÇÃO DO DESASTRE MINERÁRIO DA SAMARCO EM MARIANA</t>
+          <t>RECUPERAÇÃO E COMPENSAÇÃO DOS DANOS EM FUNÇÃO DO DESASTRE MINERÁRIO DA VALE S.A EM BRUMADINHO</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7672,31 +7002,33 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL VALE</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>ANEXO 12</t>
-        </is>
-      </c>
-      <c r="AD63" t="n">
-        <v>9468055</v>
+          <t>RESSARCIMENTOS E CONTRATAÇÕES TEMPORÁRIAS</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9288191 </t>
+        </is>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas Lista 3</t>
+          <t>RESSARCIMENTOS DE DESPESAS PÚBLICAS</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9468055 - Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas Lista 3</t>
+          <t>ACORDO JUDICIAL VALE - RESSARCIMENTOS E CONTRATAÇÕES TEMPORÁRIAS - 9288191  - RESSARCIMENTOS DE DESPESAS PÚBLICAS</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B64" t="n">
         <v>1500</v>
@@ -7709,9 +7041,6 @@
       <c r="D64" t="n">
         <v>3</v>
       </c>
-      <c r="E64" t="n">
-        <v>0</v>
-      </c>
       <c r="F64" t="n">
         <v>1501</v>
       </c>
@@ -7724,13 +7053,13 @@
         <v>3</v>
       </c>
       <c r="I64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>90</v>
       </c>
       <c r="K64" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="L64" t="n">
         <v>80</v>
@@ -7738,9 +7067,6 @@
       <c r="M64" t="n">
         <v>1</v>
       </c>
-      <c r="N64" t="n">
-        <v>10819</v>
-      </c>
       <c r="O64" t="n">
         <v>4</v>
       </c>
@@ -7748,45 +7074,39 @@
         <v>122</v>
       </c>
       <c r="Q64" t="n">
-        <v>155</v>
+        <v>705</v>
       </c>
       <c r="R64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S64" t="n">
-        <v>461</v>
+        <v>417</v>
       </c>
       <c r="T64" t="n">
-        <v>4461</v>
+        <v>2417</v>
       </c>
       <c r="U64" t="n">
         <v>1</v>
       </c>
-      <c r="V64" t="n">
-        <v>50000</v>
-      </c>
-      <c r="W64" t="n">
-        <v>50000</v>
-      </c>
       <c r="X64" t="n">
-        <v>50000</v>
+        <v>570000</v>
       </c>
       <c r="Y64" t="n">
         <v>0</v>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO E COMPENSAÇÃO DOS DANOS EM FUNÇÃO DO DESASTRE MINERÁRIO DA SAMARCO EM MARIANA</t>
+          <t>REMUNERAÇÃO DE PESSOAL ATIVO E ENCARGOS SOCIAIS</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>REPARAÇÃO DOS DANOS DOS ROMPIMENTOS EM BRUMADINHO E MARIANA</t>
+          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -7794,23 +7114,25 @@
           <t>ANEXO 12</t>
         </is>
       </c>
-      <c r="AD64" t="n">
-        <v>9468055</v>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>9468055</t>
+        </is>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas Lista 3</t>
+          <t>SUPORTE GERENCIAL, ADMINISTRATIVO, TECNOLÓGICO E DE COMUNICAÇÃO SOCIAL À IMPLEMENTAÇÃO DAS INICIATIVAS LISTA 3</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9468055 - Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas Lista 3</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9468055 - SUPORTE GERENCIAL, ADMINISTRATIVO, TECNOLÓGICO E DE COMUNICAÇÃO SOCIAL À IMPLEMENTAÇÃO DAS INICIATIVAS LISTA 3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B65" t="n">
         <v>1500</v>
@@ -7823,9 +7145,6 @@
       <c r="D65" t="n">
         <v>3</v>
       </c>
-      <c r="E65" t="n">
-        <v>0</v>
-      </c>
       <c r="F65" t="n">
         <v>1501</v>
       </c>
@@ -7838,22 +7157,19 @@
         <v>3</v>
       </c>
       <c r="I65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>90</v>
       </c>
       <c r="K65" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="L65" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="M65" t="n">
         <v>1</v>
-      </c>
-      <c r="N65" t="n">
-        <v>10819</v>
       </c>
       <c r="O65" t="n">
         <v>4</v>
@@ -7862,103 +7178,96 @@
         <v>122</v>
       </c>
       <c r="Q65" t="n">
-        <v>155</v>
+        <v>705</v>
       </c>
       <c r="R65" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S65" t="n">
-        <v>461</v>
+        <v>417</v>
       </c>
       <c r="T65" t="n">
-        <v>4461</v>
+        <v>2417</v>
       </c>
       <c r="U65" t="n">
         <v>1</v>
       </c>
-      <c r="V65" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="W65" t="n">
-        <v>2000000</v>
-      </c>
       <c r="X65" t="n">
-        <v>2000000</v>
+        <v>749000</v>
       </c>
       <c r="Y65" t="n">
         <v>0</v>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO E COMPENSAÇÃO DOS DANOS EM FUNÇÃO DO DESASTRE MINERÁRIO DA SAMARCO EM MARIANA</t>
+          <t>REMUNERAÇÃO DE PESSOAL ATIVO E ENCARGOS SOCIAIS</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>REPARAÇÃO DOS DANOS DOS ROMPIMENTOS EM BRUMADINHO E MARIANA</t>
+          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL VALE</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>ANEXO 12</t>
-        </is>
-      </c>
-      <c r="AD65" t="n">
-        <v>9468055</v>
+          <t>RESSARCIMENTOS E CONTRATAÇÕES TEMPORÁRIAS</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9288191 </t>
+        </is>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas Lista 3</t>
+          <t>RESSARCIMENTOS DE DESPESAS PÚBLICAS</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9468055 - Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas Lista 3</t>
+          <t>ACORDO JUDICIAL VALE - RESSARCIMENTOS E CONTRATAÇÕES TEMPORÁRIAS - 9288191  - RESSARCIMENTOS DE DESPESAS PÚBLICAS</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B66" t="n">
-        <v>1500</v>
+        <v>1510</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>POLÍCIA CIVIL DO ESTADO DE MINAS GERAIS - PCMG</t>
         </is>
       </c>
       <c r="D66" t="n">
         <v>3</v>
       </c>
-      <c r="E66" t="n">
-        <v>0</v>
-      </c>
       <c r="F66" t="n">
-        <v>1501</v>
+        <v>1511</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>POLÍCIA CIVIL DO ESTADO DE MINAS GERAIS - PCMG</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J66" t="n">
         <v>90</v>
       </c>
       <c r="K66" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="L66" t="n">
         <v>80</v>
@@ -7966,55 +7275,46 @@
       <c r="M66" t="n">
         <v>1</v>
       </c>
-      <c r="N66" t="n">
-        <v>10819</v>
-      </c>
       <c r="O66" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P66" t="n">
-        <v>122</v>
+        <v>181</v>
       </c>
       <c r="Q66" t="n">
-        <v>155</v>
+        <v>32</v>
       </c>
       <c r="R66" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S66" t="n">
-        <v>461</v>
+        <v>6</v>
       </c>
       <c r="T66" t="n">
-        <v>4461</v>
+        <v>1006</v>
       </c>
       <c r="U66" t="n">
         <v>1</v>
       </c>
-      <c r="V66" t="n">
-        <v>13596679</v>
-      </c>
-      <c r="W66" t="n">
-        <v>13596679</v>
-      </c>
       <c r="X66" t="n">
-        <v>13596679</v>
+        <v>1000000</v>
       </c>
       <c r="Y66" t="n">
         <v>0</v>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO E COMPENSAÇÃO DOS DANOS EM FUNÇÃO DO DESASTRE MINERÁRIO DA SAMARCO EM MARIANA</t>
+          <t>ENFRENTAMENTO À VIOLÊNCIA CONTRA A MULHER</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>REPARAÇÃO DOS DANOS DOS ROMPIMENTOS EM BRUMADINHO E MARIANA</t>
+          <t>INVESTIGAÇÃO</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -8022,57 +7322,56 @@
           <t>ANEXO 12</t>
         </is>
       </c>
-      <c r="AD66" t="n">
-        <v>9468055</v>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>9519702</t>
+        </is>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas Lista 3</t>
+          <t>Fortalecimento da infraestrutura e logística das unidades das forças de segurança</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9468055 - Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas Lista 3</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9519702 - Fortalecimento da infraestrutura e logística das unidades das forças de segurança</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B67" t="n">
-        <v>1500</v>
+        <v>1510</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>POLÍCIA CIVIL DO ESTADO DE MINAS GERAIS - PCMG</t>
         </is>
       </c>
       <c r="D67" t="n">
         <v>3</v>
       </c>
-      <c r="E67" t="n">
-        <v>0</v>
-      </c>
       <c r="F67" t="n">
-        <v>1501</v>
+        <v>1511</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>POLÍCIA CIVIL DO ESTADO DE MINAS GERAIS - PCMG</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J67" t="n">
         <v>90</v>
       </c>
       <c r="K67" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="L67" t="n">
         <v>80</v>
@@ -8080,55 +7379,46 @@
       <c r="M67" t="n">
         <v>1</v>
       </c>
-      <c r="N67" t="n">
-        <v>10819</v>
-      </c>
       <c r="O67" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P67" t="n">
-        <v>122</v>
+        <v>181</v>
       </c>
       <c r="Q67" t="n">
-        <v>155</v>
+        <v>32</v>
       </c>
       <c r="R67" t="n">
         <v>4</v>
       </c>
       <c r="S67" t="n">
-        <v>461</v>
+        <v>63</v>
       </c>
       <c r="T67" t="n">
-        <v>4461</v>
+        <v>4063</v>
       </c>
       <c r="U67" t="n">
         <v>1</v>
       </c>
-      <c r="V67" t="n">
-        <v>152100</v>
-      </c>
-      <c r="W67" t="n">
-        <v>152100</v>
-      </c>
       <c r="X67" t="n">
-        <v>152100</v>
+        <v>20000000</v>
       </c>
       <c r="Y67" t="n">
         <v>0</v>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>RECUPERAÇÃO E COMPENSAÇÃO DOS DANOS EM FUNÇÃO DO DESASTRE MINERÁRIO DA SAMARCO EM MARIANA</t>
+          <t>CONSTRUÇÃO NÚCLEO INTEGRADO DE PERÍCIAS</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>REPARAÇÃO DOS DANOS DOS ROMPIMENTOS EM BRUMADINHO E MARIANA</t>
+          <t>INVESTIGAÇÃO</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -8136,131 +7426,19 @@
           <t>ANEXO 12</t>
         </is>
       </c>
-      <c r="AD67" t="n">
-        <v>9468055</v>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>9494511</t>
+        </is>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas Lista 3</t>
+          <t>Fortalecimento da infraestrutura e logística das unidades das forças de segurança</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>Acordo Judicial do Rio Doce - ANEXO 12 - 9468055 - Suporte gerencial, administrativo, tecnológico e de comunicação social à implementação das iniciativas Lista 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B68" t="n">
-        <v>1500</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>3</v>
-      </c>
-      <c r="E68" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" t="n">
-        <v>1501</v>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
-        </is>
-      </c>
-      <c r="H68" t="n">
-        <v>3</v>
-      </c>
-      <c r="I68" t="n">
-        <v>3</v>
-      </c>
-      <c r="J68" t="n">
-        <v>90</v>
-      </c>
-      <c r="K68" t="n">
-        <v>37</v>
-      </c>
-      <c r="L68" t="n">
-        <v>95</v>
-      </c>
-      <c r="M68" t="n">
-        <v>1</v>
-      </c>
-      <c r="N68" t="n">
-        <v>10821</v>
-      </c>
-      <c r="O68" t="n">
-        <v>4</v>
-      </c>
-      <c r="P68" t="n">
-        <v>122</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>155</v>
-      </c>
-      <c r="R68" t="n">
-        <v>4</v>
-      </c>
-      <c r="S68" t="n">
-        <v>462</v>
-      </c>
-      <c r="T68" t="n">
-        <v>4462</v>
-      </c>
-      <c r="U68" t="n">
-        <v>1</v>
-      </c>
-      <c r="V68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="W68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="X68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>RECUPERAÇÃO E COMPENSAÇÃO DOS DANOS EM FUNÇÃO DO DESASTRE MINERÁRIO DA VALE S.A EM BRUMADINHO</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>REPARAÇÃO DOS DANOS DOS ROMPIMENTOS EM BRUMADINHO E MARIANA</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>Acordo Judicial Vale</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ressarcimentos e contratações temporárias</t>
-        </is>
-      </c>
-      <c r="AD68" t="n">
-        <v>9288191</v>
-      </c>
-      <c r="AE68" t="inlineStr">
-        <is>
-          <t>Ressarcimentos de despesas públicas</t>
-        </is>
-      </c>
-      <c r="AF68" t="inlineStr">
-        <is>
-          <t>Acordo Judicial Vale - Ressarcimentos e contratações temporárias - 9288191 - Ressarcimentos de despesas públicas</t>
+          <t>ACORDO JUDICIAL DO RIO DOCE - ANEXO 12 - 9494511 - Fortalecimento da infraestrutura e logística das unidades das forças de segurança</t>
         </is>
       </c>
     </row>
